--- a/public/Plantilla_Agenda.xlsx
+++ b/public/Plantilla_Agenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jrive\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5BCFEE-E078-4A59-8A61-107993B66DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAA655B-D806-412A-945D-29DE133BE868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -438,7 +438,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -916,11 +916,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="162">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -945,12 +958,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1084,159 +1091,64 @@
     <xf numFmtId="1" fontId="10" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="26" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="8" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1264,62 +1176,167 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="26" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1343,9 +1360,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
+      <xdr:colOff>323850</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="857250" cy="704850"/>
     <xdr:pic>
@@ -1366,6 +1383,10 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="323850" y="66675"/>
+          <a:ext cx="857250" cy="704850"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -1594,49 +1615,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="125"/>
-      <c r="B1" s="126"/>
-      <c r="C1" s="131" t="s">
+      <c r="A1" s="84"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
-      <c r="H1" s="133"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="92"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="127"/>
-      <c r="B2" s="128"/>
-      <c r="C2" s="134"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="136"/>
+      <c r="A2" s="86"/>
+      <c r="B2" s="87"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="95"/>
     </row>
     <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="127"/>
-      <c r="B3" s="128"/>
-      <c r="C3" s="137"/>
-      <c r="D3" s="138"/>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="138"/>
-      <c r="H3" s="139"/>
+      <c r="A3" s="86"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="96"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="97"/>
+      <c r="F3" s="97"/>
+      <c r="G3" s="97"/>
+      <c r="H3" s="98"/>
     </row>
     <row r="4" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="129"/>
-      <c r="B4" s="130"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D4" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="140"/>
-      <c r="F4" s="120"/>
-      <c r="G4" s="118"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="100"/>
       <c r="H4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1652,16 +1673,16 @@
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="141" t="s">
+      <c r="A6" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="123"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="142"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="103"/>
+      <c r="H6" s="104"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
@@ -1685,15 +1706,15 @@
       <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="123"/>
-      <c r="C7" s="120"/>
-      <c r="D7" s="120"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
       <c r="E7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="123"/>
-      <c r="G7" s="120"/>
-      <c r="H7" s="142"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="104"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6"/>
@@ -1717,15 +1738,15 @@
       <c r="A8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="124"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="82"/>
+      <c r="D8" s="82"/>
       <c r="E8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="123"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="142"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="104"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
@@ -1746,3343 +1767,3343 @@
       <c r="Z8" s="6"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="146"/>
-      <c r="B9" s="85"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="86"/>
+      <c r="A9" s="108"/>
+      <c r="B9" s="109"/>
+      <c r="C9" s="109"/>
+      <c r="D9" s="109"/>
+      <c r="E9" s="109"/>
+      <c r="F9" s="109"/>
+      <c r="G9" s="109"/>
+      <c r="H9" s="110"/>
     </row>
     <row r="10" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="147" t="s">
+      <c r="A10" s="111" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
-      <c r="G10" s="71"/>
-      <c r="H10" s="88"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="112"/>
     </row>
     <row r="11" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="148"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="98"/>
-      <c r="G11" s="98"/>
-      <c r="H11" s="99"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="114"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="114"/>
+      <c r="G11" s="114"/>
+      <c r="H11" s="115"/>
     </row>
     <row r="12" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="149" t="s">
+      <c r="A12" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="90"/>
-      <c r="C12" s="90"/>
-      <c r="D12" s="90"/>
-      <c r="E12" s="90"/>
-      <c r="F12" s="90"/>
-      <c r="G12" s="90"/>
-      <c r="H12" s="91"/>
+      <c r="B12" s="117"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="118"/>
     </row>
     <row r="13" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="150" t="s">
+      <c r="A13" s="119" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="144"/>
-      <c r="C13" s="11" t="s">
+      <c r="B13" s="106"/>
+      <c r="C13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="143" t="s">
+      <c r="F13" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="144"/>
-      <c r="H13" s="13" t="s">
+      <c r="G13" s="106"/>
+      <c r="H13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="14"/>
-      <c r="R13" s="14"/>
-      <c r="S13" s="14"/>
-      <c r="T13" s="14"/>
-      <c r="U13" s="14"/>
-      <c r="V13" s="14"/>
-      <c r="W13" s="14"/>
-      <c r="X13" s="14"/>
-      <c r="Y13" s="14"/>
-      <c r="Z13" s="14"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="12"/>
+      <c r="R13" s="12"/>
+      <c r="S13" s="12"/>
+      <c r="T13" s="12"/>
+      <c r="U13" s="12"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="12"/>
+      <c r="X13" s="12"/>
+      <c r="Y13" s="12"/>
+      <c r="Z13" s="12"/>
     </row>
     <row r="14" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="151"/>
-      <c r="B14" s="158"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="145"/>
-      <c r="G14" s="158"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="14"/>
-      <c r="R14" s="14"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
-      <c r="W14" s="14"/>
-      <c r="X14" s="14"/>
-      <c r="Y14" s="14"/>
-      <c r="Z14" s="14"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="77"/>
+      <c r="G14" s="107"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="12"/>
+      <c r="R14" s="12"/>
+      <c r="S14" s="12"/>
+      <c r="T14" s="12"/>
+      <c r="U14" s="12"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="12"/>
+      <c r="X14" s="12"/>
+      <c r="Y14" s="12"/>
+      <c r="Z14" s="12"/>
     </row>
     <row r="15" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="151"/>
-      <c r="B15" s="152"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="145"/>
-      <c r="G15" s="152"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
-      <c r="Q15" s="14"/>
-      <c r="R15" s="14"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="14"/>
-      <c r="U15" s="14"/>
-      <c r="V15" s="14"/>
-      <c r="W15" s="14"/>
-      <c r="X15" s="14"/>
-      <c r="Y15" s="14"/>
-      <c r="Z15" s="14"/>
+      <c r="A15" s="72"/>
+      <c r="B15" s="73"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="12"/>
+      <c r="R15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
     </row>
     <row r="16" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="151"/>
-      <c r="B16" s="152"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="145"/>
-      <c r="G16" s="152"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="14"/>
-      <c r="R16" s="14"/>
-      <c r="S16" s="14"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="14"/>
-      <c r="V16" s="14"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14"/>
-      <c r="Y16" s="14"/>
-      <c r="Z16" s="14"/>
+      <c r="A16" s="72"/>
+      <c r="B16" s="73"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="12"/>
+      <c r="R16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="12"/>
     </row>
     <row r="17" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="151"/>
-      <c r="B17" s="152"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="145"/>
-      <c r="G17" s="152"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
+      <c r="A17" s="72"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="12"/>
+      <c r="R17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="12"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="12"/>
+      <c r="Z17" s="12"/>
     </row>
     <row r="18" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="151"/>
-      <c r="B18" s="152"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="145"/>
-      <c r="G18" s="152"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14"/>
-      <c r="Z18" s="14"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="12"/>
     </row>
     <row r="19" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="151"/>
-      <c r="B19" s="152"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="145"/>
-      <c r="G19" s="152"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="12"/>
     </row>
     <row r="20" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="157"/>
-      <c r="B20" s="152"/>
-      <c r="C20" s="49"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="145"/>
-      <c r="G20" s="152"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
     </row>
     <row r="21" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="157"/>
-      <c r="B21" s="152"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49"/>
-      <c r="E21" s="49"/>
-      <c r="F21" s="145"/>
-      <c r="G21" s="152"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
+      <c r="A21" s="78"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="12"/>
     </row>
     <row r="22" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="157"/>
-      <c r="B22" s="152"/>
-      <c r="C22" s="49"/>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49"/>
-      <c r="F22" s="145"/>
-      <c r="G22" s="152"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
+      <c r="A22" s="78"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="47"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="47"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12"/>
     </row>
     <row r="23" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="157"/>
-      <c r="B23" s="152"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
-      <c r="E23" s="49"/>
-      <c r="F23" s="145"/>
-      <c r="G23" s="152"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="77"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
+      <c r="Z23" s="12"/>
     </row>
     <row r="24" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="155"/>
-      <c r="B24" s="156"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="49"/>
-      <c r="F24" s="145"/>
-      <c r="G24" s="152"/>
-      <c r="H24" s="50"/>
+      <c r="A24" s="74"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="77"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="48"/>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A25" s="153" t="s">
+      <c r="A25" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="122"/>
-      <c r="F25" s="154">
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="69">
         <f>SUM(F14:G24)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="69"/>
-      <c r="H25" s="47">
+      <c r="G25" s="70"/>
+      <c r="H25" s="45">
         <f>SUM(H14:H24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
+      <c r="A26" s="13"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="17"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="15"/>
     </row>
     <row r="27" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="70" t="s">
+      <c r="A27" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="71"/>
-      <c r="C27" s="69"/>
-      <c r="D27" s="18" t="s">
+      <c r="B27" s="67"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="68" t="s">
+      <c r="F27" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="69"/>
-      <c r="H27" s="19" t="s">
+      <c r="G27" s="70"/>
+      <c r="H27" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="20"/>
-      <c r="Q27" s="20"/>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="20"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
+      <c r="W27" s="18"/>
+      <c r="X27" s="18"/>
+      <c r="Y27" s="18"/>
+      <c r="Z27" s="18"/>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="115" t="s">
+      <c r="A28" s="122" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="71"/>
-      <c r="C28" s="69"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="69"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-      <c r="U28" s="20"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="20"/>
-      <c r="X28" s="20"/>
-      <c r="Y28" s="20"/>
-      <c r="Z28" s="20"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="Q28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="18"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
+      <c r="W28" s="18"/>
+      <c r="X28" s="18"/>
+      <c r="Y28" s="18"/>
+      <c r="Z28" s="18"/>
     </row>
     <row r="29" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="65"/>
-      <c r="B29" s="72"/>
-      <c r="C29" s="73"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="76"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
+      <c r="A29" s="123"/>
+      <c r="B29" s="124"/>
+      <c r="C29" s="125"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="79"/>
+      <c r="G29" s="121"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
     </row>
     <row r="30" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="65"/>
-      <c r="B30" s="66"/>
-      <c r="C30" s="67"/>
-      <c r="D30" s="62"/>
-      <c r="E30" s="62"/>
-      <c r="F30" s="76"/>
-      <c r="G30" s="82"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
+      <c r="A30" s="123"/>
+      <c r="B30" s="155"/>
+      <c r="C30" s="156"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="79"/>
+      <c r="G30" s="157"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
     </row>
     <row r="31" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="65"/>
-      <c r="B31" s="66"/>
-      <c r="C31" s="67"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="62"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
+      <c r="A31" s="123"/>
+      <c r="B31" s="155"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="79"/>
+      <c r="G31" s="80"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
     </row>
     <row r="32" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="65"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="159"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="51"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="28"/>
+      <c r="A32" s="123"/>
+      <c r="B32" s="124"/>
+      <c r="C32" s="125"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="79"/>
+      <c r="G32" s="121"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="26"/>
     </row>
     <row r="33" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="65"/>
-      <c r="B33" s="72"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="63"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="51"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="27"/>
+      <c r="A33" s="123"/>
+      <c r="B33" s="124"/>
+      <c r="C33" s="125"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="128"/>
+      <c r="G33" s="121"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="25"/>
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="78" t="s">
+      <c r="A34" s="162" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="71"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="160">
+      <c r="B34" s="67"/>
+      <c r="C34" s="70"/>
+      <c r="D34" s="62">
         <f>SUM(D29:D33)</f>
         <v>0</v>
       </c>
-      <c r="E34" s="160">
+      <c r="E34" s="62">
         <f>SUM(E29:E33)</f>
         <v>0</v>
       </c>
-      <c r="F34" s="75"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="27"/>
+      <c r="F34" s="161"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="23"/>
+      <c r="I34" s="27"/>
+      <c r="J34" s="25"/>
     </row>
     <row r="35" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="65"/>
-      <c r="B35" s="72"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="159"/>
-      <c r="E35" s="62"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="27"/>
+      <c r="A35" s="123"/>
+      <c r="B35" s="124"/>
+      <c r="C35" s="125"/>
+      <c r="D35" s="61"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="121"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="25"/>
     </row>
     <row r="36" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="65"/>
-      <c r="B36" s="66"/>
-      <c r="C36" s="67"/>
-      <c r="D36" s="159"/>
-      <c r="E36" s="62"/>
-      <c r="F36" s="76"/>
-      <c r="G36" s="81"/>
-      <c r="H36" s="51"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="27"/>
+      <c r="A36" s="123"/>
+      <c r="B36" s="155"/>
+      <c r="C36" s="156"/>
+      <c r="D36" s="61"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="80"/>
+      <c r="H36" s="49"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="25"/>
     </row>
     <row r="37" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="65"/>
-      <c r="B37" s="66"/>
-      <c r="C37" s="67"/>
-      <c r="D37" s="159"/>
-      <c r="E37" s="62"/>
-      <c r="F37" s="76"/>
-      <c r="G37" s="81"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="27"/>
+      <c r="A37" s="123"/>
+      <c r="B37" s="155"/>
+      <c r="C37" s="156"/>
+      <c r="D37" s="61"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="49"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="25"/>
     </row>
     <row r="38" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="79"/>
-      <c r="B38" s="72"/>
-      <c r="C38" s="73"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="62"/>
-      <c r="F38" s="63"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="51"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="27"/>
+      <c r="A38" s="163"/>
+      <c r="B38" s="124"/>
+      <c r="C38" s="125"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="128"/>
+      <c r="G38" s="121"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="25"/>
     </row>
     <row r="39" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="65"/>
-      <c r="B39" s="72"/>
-      <c r="C39" s="73"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="62"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="74"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="27"/>
+      <c r="A39" s="123"/>
+      <c r="B39" s="124"/>
+      <c r="C39" s="125"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="128"/>
+      <c r="G39" s="121"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="25"/>
     </row>
     <row r="40" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="80" t="s">
+      <c r="A40" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="B40" s="71"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="30">
+      <c r="B40" s="67"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="28">
         <f>SUM(D34:D39)</f>
         <v>0</v>
       </c>
-      <c r="E40" s="30">
+      <c r="E40" s="28">
         <f>SUM(E34:E39)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="77"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="31"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="27"/>
+      <c r="F40" s="131"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="25"/>
     </row>
     <row r="41" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="116"/>
-      <c r="B41" s="98"/>
-      <c r="C41" s="98"/>
-      <c r="D41" s="98"/>
-      <c r="E41" s="98"/>
-      <c r="F41" s="98"/>
-      <c r="G41" s="98"/>
-      <c r="H41" s="99"/>
+      <c r="A41" s="126"/>
+      <c r="B41" s="114"/>
+      <c r="C41" s="114"/>
+      <c r="D41" s="114"/>
+      <c r="E41" s="114"/>
+      <c r="F41" s="114"/>
+      <c r="G41" s="114"/>
+      <c r="H41" s="115"/>
     </row>
     <row r="42" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="87" t="s">
+      <c r="A42" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="71"/>
-      <c r="F42" s="71"/>
-      <c r="G42" s="71"/>
-      <c r="H42" s="88"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="112"/>
     </row>
     <row r="43" spans="1:26" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="70" t="s">
+      <c r="A43" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="B43" s="71"/>
-      <c r="C43" s="69"/>
-      <c r="D43" s="18" t="s">
+      <c r="B43" s="67"/>
+      <c r="C43" s="70"/>
+      <c r="D43" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E43" s="18" t="s">
+      <c r="E43" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F43" s="68" t="s">
+      <c r="F43" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="G43" s="69"/>
-      <c r="H43" s="19" t="s">
+      <c r="G43" s="70"/>
+      <c r="H43" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="20"/>
-      <c r="O43" s="20"/>
-      <c r="P43" s="20"/>
-      <c r="Q43" s="20"/>
-      <c r="R43" s="20"/>
-      <c r="S43" s="20"/>
-      <c r="T43" s="20"/>
-      <c r="U43" s="20"/>
-      <c r="V43" s="20"/>
-      <c r="W43" s="20"/>
-      <c r="X43" s="20"/>
-      <c r="Y43" s="20"/>
-      <c r="Z43" s="20"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18"/>
+      <c r="R43" s="18"/>
+      <c r="S43" s="18"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="18"/>
+      <c r="V43" s="18"/>
+      <c r="W43" s="18"/>
+      <c r="X43" s="18"/>
+      <c r="Y43" s="18"/>
+      <c r="Z43" s="18"/>
     </row>
     <row r="44" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="65"/>
-      <c r="B44" s="72"/>
-      <c r="C44" s="73"/>
-      <c r="D44" s="61"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="63"/>
-      <c r="G44" s="74"/>
-      <c r="H44" s="52"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="20"/>
-      <c r="O44" s="20"/>
-      <c r="P44" s="20"/>
-      <c r="Q44" s="20"/>
-      <c r="R44" s="20"/>
-      <c r="S44" s="20"/>
-      <c r="T44" s="20"/>
-      <c r="U44" s="20"/>
-      <c r="V44" s="20"/>
-      <c r="W44" s="20"/>
-      <c r="X44" s="20"/>
-      <c r="Y44" s="20"/>
-      <c r="Z44" s="20"/>
+      <c r="A44" s="123"/>
+      <c r="B44" s="124"/>
+      <c r="C44" s="125"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="128"/>
+      <c r="G44" s="121"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+      <c r="L44" s="18"/>
+      <c r="M44" s="18"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="18"/>
+      <c r="R44" s="18"/>
+      <c r="S44" s="18"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="18"/>
+      <c r="V44" s="18"/>
+      <c r="W44" s="18"/>
+      <c r="X44" s="18"/>
+      <c r="Y44" s="18"/>
+      <c r="Z44" s="18"/>
     </row>
     <row r="45" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="65"/>
-      <c r="B45" s="72"/>
-      <c r="C45" s="73"/>
-      <c r="D45" s="61"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="63"/>
-      <c r="G45" s="74"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="20"/>
-      <c r="P45" s="20"/>
-      <c r="Q45" s="20"/>
-      <c r="R45" s="20"/>
-      <c r="S45" s="20"/>
-      <c r="T45" s="20"/>
-      <c r="U45" s="20"/>
-      <c r="V45" s="20"/>
-      <c r="W45" s="20"/>
-      <c r="X45" s="20"/>
-      <c r="Y45" s="20"/>
-      <c r="Z45" s="20"/>
+      <c r="A45" s="123"/>
+      <c r="B45" s="124"/>
+      <c r="C45" s="125"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="128"/>
+      <c r="G45" s="121"/>
+      <c r="H45" s="50"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="18"/>
+      <c r="X45" s="18"/>
+      <c r="Y45" s="18"/>
+      <c r="Z45" s="18"/>
     </row>
     <row r="46" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="65"/>
-      <c r="B46" s="72"/>
-      <c r="C46" s="73"/>
-      <c r="D46" s="61"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="74"/>
-      <c r="H46" s="52"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
+      <c r="A46" s="123"/>
+      <c r="B46" s="124"/>
+      <c r="C46" s="125"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="79"/>
+      <c r="G46" s="121"/>
+      <c r="H46" s="50"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
     </row>
     <row r="47" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="65"/>
-      <c r="B47" s="72"/>
-      <c r="C47" s="73"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="63"/>
-      <c r="G47" s="74"/>
-      <c r="H47" s="52"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
+      <c r="A47" s="123"/>
+      <c r="B47" s="124"/>
+      <c r="C47" s="125"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="128"/>
+      <c r="G47" s="121"/>
+      <c r="H47" s="50"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="31"/>
+      <c r="K47" s="31"/>
     </row>
     <row r="48" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="65"/>
-      <c r="B48" s="72"/>
-      <c r="C48" s="73"/>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="76"/>
-      <c r="G48" s="74"/>
-      <c r="H48" s="52"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
+      <c r="A48" s="123"/>
+      <c r="B48" s="124"/>
+      <c r="C48" s="125"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="79"/>
+      <c r="G48" s="121"/>
+      <c r="H48" s="50"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
     </row>
     <row r="49" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="80" t="s">
+      <c r="A49" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="B49" s="71"/>
-      <c r="C49" s="69"/>
-      <c r="D49" s="34">
+      <c r="B49" s="67"/>
+      <c r="C49" s="70"/>
+      <c r="D49" s="32">
         <f>SUM(D44:D48)</f>
         <v>0</v>
       </c>
-      <c r="E49" s="35">
+      <c r="E49" s="33">
         <f>SUM(E44:E48)</f>
         <v>0</v>
       </c>
-      <c r="F49" s="83"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="31"/>
+      <c r="F49" s="134"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="29"/>
     </row>
     <row r="50" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="84"/>
-      <c r="B50" s="85"/>
-      <c r="C50" s="85"/>
-      <c r="D50" s="85"/>
-      <c r="E50" s="85"/>
-      <c r="F50" s="85"/>
-      <c r="G50" s="85"/>
-      <c r="H50" s="86"/>
+      <c r="A50" s="158"/>
+      <c r="B50" s="109"/>
+      <c r="C50" s="109"/>
+      <c r="D50" s="109"/>
+      <c r="E50" s="109"/>
+      <c r="F50" s="109"/>
+      <c r="G50" s="109"/>
+      <c r="H50" s="110"/>
     </row>
     <row r="51" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="87" t="s">
+      <c r="A51" s="127" t="s">
         <v>26</v>
       </c>
-      <c r="B51" s="71"/>
-      <c r="C51" s="71"/>
-      <c r="D51" s="71"/>
-      <c r="E51" s="71"/>
-      <c r="F51" s="71"/>
-      <c r="G51" s="71"/>
-      <c r="H51" s="88"/>
+      <c r="B51" s="67"/>
+      <c r="C51" s="67"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="67"/>
+      <c r="F51" s="67"/>
+      <c r="G51" s="67"/>
+      <c r="H51" s="112"/>
     </row>
     <row r="52" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="89" t="s">
+      <c r="A52" s="159" t="s">
         <v>27</v>
       </c>
-      <c r="B52" s="90"/>
-      <c r="C52" s="90"/>
-      <c r="D52" s="90"/>
-      <c r="E52" s="90"/>
-      <c r="F52" s="90"/>
-      <c r="G52" s="90"/>
-      <c r="H52" s="91"/>
+      <c r="B52" s="117"/>
+      <c r="C52" s="117"/>
+      <c r="D52" s="117"/>
+      <c r="E52" s="117"/>
+      <c r="F52" s="117"/>
+      <c r="G52" s="117"/>
+      <c r="H52" s="118"/>
     </row>
     <row r="53" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="70" t="s">
+      <c r="A53" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="B53" s="71"/>
-      <c r="C53" s="69"/>
-      <c r="D53" s="18" t="s">
+      <c r="B53" s="67"/>
+      <c r="C53" s="70"/>
+      <c r="D53" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F53" s="68" t="s">
+      <c r="F53" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="G53" s="69"/>
-      <c r="H53" s="19" t="s">
+      <c r="G53" s="70"/>
+      <c r="H53" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="65"/>
-      <c r="B54" s="72"/>
-      <c r="C54" s="73"/>
-      <c r="D54" s="61"/>
-      <c r="E54" s="61"/>
-      <c r="F54" s="63"/>
-      <c r="G54" s="74"/>
-      <c r="H54" s="52"/>
+      <c r="A54" s="123"/>
+      <c r="B54" s="124"/>
+      <c r="C54" s="125"/>
+      <c r="D54" s="59"/>
+      <c r="E54" s="59"/>
+      <c r="F54" s="128"/>
+      <c r="G54" s="121"/>
+      <c r="H54" s="50"/>
     </row>
     <row r="55" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="65"/>
-      <c r="B55" s="66"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="63"/>
-      <c r="G55" s="64"/>
-      <c r="H55" s="52"/>
+      <c r="A55" s="123"/>
+      <c r="B55" s="155"/>
+      <c r="C55" s="156"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="128"/>
+      <c r="G55" s="160"/>
+      <c r="H55" s="50"/>
     </row>
     <row r="56" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="65"/>
-      <c r="B56" s="66"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="61"/>
-      <c r="F56" s="63"/>
-      <c r="G56" s="64"/>
-      <c r="H56" s="52"/>
+      <c r="A56" s="123"/>
+      <c r="B56" s="155"/>
+      <c r="C56" s="156"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="59"/>
+      <c r="F56" s="128"/>
+      <c r="G56" s="160"/>
+      <c r="H56" s="50"/>
     </row>
     <row r="57" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="65"/>
-      <c r="B57" s="72"/>
-      <c r="C57" s="73"/>
-      <c r="D57" s="61"/>
-      <c r="E57" s="61"/>
-      <c r="F57" s="63"/>
-      <c r="G57" s="74"/>
-      <c r="H57" s="52"/>
+      <c r="A57" s="123"/>
+      <c r="B57" s="124"/>
+      <c r="C57" s="125"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="128"/>
+      <c r="G57" s="121"/>
+      <c r="H57" s="50"/>
     </row>
     <row r="58" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="65"/>
-      <c r="B58" s="72"/>
-      <c r="C58" s="73"/>
-      <c r="D58" s="61"/>
-      <c r="E58" s="61"/>
-      <c r="F58" s="63"/>
-      <c r="G58" s="74"/>
-      <c r="H58" s="52"/>
-      <c r="J58" s="54"/>
+      <c r="A58" s="123"/>
+      <c r="B58" s="124"/>
+      <c r="C58" s="125"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="128"/>
+      <c r="G58" s="121"/>
+      <c r="H58" s="50"/>
+      <c r="J58" s="52"/>
     </row>
     <row r="59" spans="1:10" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="119" t="s">
+      <c r="A59" s="132" t="s">
         <v>28</v>
       </c>
-      <c r="B59" s="120"/>
-      <c r="C59" s="118"/>
-      <c r="D59" s="62">
+      <c r="B59" s="82"/>
+      <c r="C59" s="100"/>
+      <c r="D59" s="60">
         <f>SUM(D54:D58)</f>
         <v>0</v>
       </c>
-      <c r="E59" s="62">
+      <c r="E59" s="60">
         <f>SUM(E54:E58)</f>
         <v>0</v>
       </c>
-      <c r="F59" s="117"/>
-      <c r="G59" s="118"/>
-      <c r="H59" s="53"/>
+      <c r="F59" s="130"/>
+      <c r="G59" s="100"/>
+      <c r="H59" s="51"/>
     </row>
     <row r="60" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="65"/>
-      <c r="B60" s="72"/>
-      <c r="C60" s="73"/>
-      <c r="D60" s="61"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="63"/>
-      <c r="G60" s="74"/>
-      <c r="H60" s="52"/>
+      <c r="A60" s="123"/>
+      <c r="B60" s="124"/>
+      <c r="C60" s="125"/>
+      <c r="D60" s="59"/>
+      <c r="E60" s="59"/>
+      <c r="F60" s="128"/>
+      <c r="G60" s="121"/>
+      <c r="H60" s="50"/>
     </row>
     <row r="61" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="65"/>
-      <c r="B61" s="66"/>
-      <c r="C61" s="67"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="63"/>
-      <c r="G61" s="64"/>
-      <c r="H61" s="52"/>
+      <c r="A61" s="123"/>
+      <c r="B61" s="155"/>
+      <c r="C61" s="156"/>
+      <c r="D61" s="59"/>
+      <c r="E61" s="59"/>
+      <c r="F61" s="128"/>
+      <c r="G61" s="160"/>
+      <c r="H61" s="50"/>
     </row>
     <row r="62" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="65"/>
-      <c r="B62" s="66"/>
-      <c r="C62" s="67"/>
-      <c r="D62" s="61"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="63"/>
-      <c r="G62" s="64"/>
-      <c r="H62" s="52"/>
+      <c r="A62" s="123"/>
+      <c r="B62" s="155"/>
+      <c r="C62" s="156"/>
+      <c r="D62" s="59"/>
+      <c r="E62" s="59"/>
+      <c r="F62" s="128"/>
+      <c r="G62" s="160"/>
+      <c r="H62" s="50"/>
     </row>
     <row r="63" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="65"/>
-      <c r="B63" s="72"/>
-      <c r="C63" s="73"/>
-      <c r="D63" s="61"/>
-      <c r="E63" s="61"/>
-      <c r="F63" s="63"/>
-      <c r="G63" s="74"/>
-      <c r="H63" s="52"/>
+      <c r="A63" s="123"/>
+      <c r="B63" s="124"/>
+      <c r="C63" s="125"/>
+      <c r="D63" s="59"/>
+      <c r="E63" s="59"/>
+      <c r="F63" s="128"/>
+      <c r="G63" s="121"/>
+      <c r="H63" s="50"/>
     </row>
     <row r="64" spans="1:10" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="65"/>
-      <c r="B64" s="72"/>
-      <c r="C64" s="73"/>
-      <c r="D64" s="61"/>
-      <c r="E64" s="61"/>
-      <c r="F64" s="63"/>
-      <c r="G64" s="74"/>
-      <c r="H64" s="52"/>
+      <c r="A64" s="123"/>
+      <c r="B64" s="124"/>
+      <c r="C64" s="125"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="59"/>
+      <c r="F64" s="128"/>
+      <c r="G64" s="121"/>
+      <c r="H64" s="50"/>
     </row>
     <row r="65" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="121" t="s">
+      <c r="A65" s="133" t="s">
         <v>18</v>
       </c>
-      <c r="B65" s="71"/>
-      <c r="C65" s="122"/>
-      <c r="D65" s="55">
+      <c r="B65" s="67"/>
+      <c r="C65" s="68"/>
+      <c r="D65" s="53">
         <f>SUM(D59:D64)</f>
         <v>0</v>
       </c>
-      <c r="E65" s="30">
+      <c r="E65" s="28">
         <f>SUM(E59:E64)</f>
         <v>0</v>
       </c>
-      <c r="F65" s="77"/>
-      <c r="G65" s="69"/>
-      <c r="H65" s="36"/>
+      <c r="F65" s="131"/>
+      <c r="G65" s="70"/>
+      <c r="H65" s="34"/>
     </row>
     <row r="66" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="92"/>
-      <c r="B66" s="85"/>
-      <c r="C66" s="85"/>
-      <c r="D66" s="85"/>
-      <c r="E66" s="85"/>
-      <c r="F66" s="85"/>
-      <c r="G66" s="85"/>
-      <c r="H66" s="86"/>
+      <c r="A66" s="136"/>
+      <c r="B66" s="109"/>
+      <c r="C66" s="109"/>
+      <c r="D66" s="109"/>
+      <c r="E66" s="109"/>
+      <c r="F66" s="109"/>
+      <c r="G66" s="109"/>
+      <c r="H66" s="110"/>
     </row>
     <row r="67" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="87" t="s">
+      <c r="A67" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="B67" s="71"/>
-      <c r="C67" s="71"/>
-      <c r="D67" s="71"/>
-      <c r="E67" s="71"/>
-      <c r="F67" s="71"/>
-      <c r="G67" s="71"/>
-      <c r="H67" s="88"/>
+      <c r="B67" s="67"/>
+      <c r="C67" s="67"/>
+      <c r="D67" s="67"/>
+      <c r="E67" s="67"/>
+      <c r="F67" s="67"/>
+      <c r="G67" s="67"/>
+      <c r="H67" s="112"/>
     </row>
     <row r="68" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="93"/>
-      <c r="B68" s="90"/>
-      <c r="C68" s="90"/>
-      <c r="D68" s="90"/>
-      <c r="E68" s="90"/>
-      <c r="F68" s="90"/>
-      <c r="G68" s="90"/>
-      <c r="H68" s="91"/>
+      <c r="A68" s="137"/>
+      <c r="B68" s="117"/>
+      <c r="C68" s="117"/>
+      <c r="D68" s="117"/>
+      <c r="E68" s="117"/>
+      <c r="F68" s="117"/>
+      <c r="G68" s="117"/>
+      <c r="H68" s="118"/>
     </row>
     <row r="69" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="70" t="s">
+      <c r="A69" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="B69" s="71"/>
-      <c r="C69" s="69"/>
-      <c r="D69" s="18" t="s">
+      <c r="B69" s="67"/>
+      <c r="C69" s="70"/>
+      <c r="D69" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E69" s="18" t="s">
+      <c r="E69" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F69" s="68" t="s">
+      <c r="F69" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="G69" s="69"/>
-      <c r="H69" s="19" t="s">
+      <c r="G69" s="70"/>
+      <c r="H69" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="65"/>
-      <c r="B70" s="72"/>
-      <c r="C70" s="73"/>
-      <c r="D70" s="62"/>
-      <c r="E70" s="62"/>
-      <c r="F70" s="63"/>
-      <c r="G70" s="74"/>
-      <c r="H70" s="52"/>
+      <c r="A70" s="123"/>
+      <c r="B70" s="124"/>
+      <c r="C70" s="125"/>
+      <c r="D70" s="60"/>
+      <c r="E70" s="60"/>
+      <c r="F70" s="128"/>
+      <c r="G70" s="121"/>
+      <c r="H70" s="50"/>
     </row>
     <row r="71" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="65"/>
-      <c r="B71" s="72"/>
-      <c r="C71" s="73"/>
-      <c r="D71" s="61"/>
-      <c r="E71" s="62"/>
-      <c r="F71" s="63"/>
-      <c r="G71" s="74"/>
-      <c r="H71" s="52"/>
+      <c r="A71" s="123"/>
+      <c r="B71" s="124"/>
+      <c r="C71" s="125"/>
+      <c r="D71" s="59"/>
+      <c r="E71" s="60"/>
+      <c r="F71" s="128"/>
+      <c r="G71" s="121"/>
+      <c r="H71" s="50"/>
     </row>
     <row r="72" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="65"/>
-      <c r="B72" s="72"/>
-      <c r="C72" s="73"/>
-      <c r="D72" s="61"/>
-      <c r="E72" s="62"/>
-      <c r="F72" s="63"/>
-      <c r="G72" s="74"/>
-      <c r="H72" s="52"/>
+      <c r="A72" s="123"/>
+      <c r="B72" s="124"/>
+      <c r="C72" s="125"/>
+      <c r="D72" s="59"/>
+      <c r="E72" s="60"/>
+      <c r="F72" s="128"/>
+      <c r="G72" s="121"/>
+      <c r="H72" s="50"/>
     </row>
     <row r="73" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="65"/>
-      <c r="B73" s="72"/>
-      <c r="C73" s="73"/>
-      <c r="D73" s="61"/>
-      <c r="E73" s="62"/>
-      <c r="F73" s="76"/>
-      <c r="G73" s="74"/>
-      <c r="H73" s="52"/>
+      <c r="A73" s="123"/>
+      <c r="B73" s="124"/>
+      <c r="C73" s="125"/>
+      <c r="D73" s="59"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="79"/>
+      <c r="G73" s="121"/>
+      <c r="H73" s="50"/>
     </row>
     <row r="74" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="65"/>
-      <c r="B74" s="72"/>
-      <c r="C74" s="73"/>
-      <c r="D74" s="62"/>
-      <c r="E74" s="62"/>
-      <c r="F74" s="63"/>
-      <c r="G74" s="74"/>
-      <c r="H74" s="52"/>
+      <c r="A74" s="123"/>
+      <c r="B74" s="124"/>
+      <c r="C74" s="125"/>
+      <c r="D74" s="60"/>
+      <c r="E74" s="60"/>
+      <c r="F74" s="128"/>
+      <c r="G74" s="121"/>
+      <c r="H74" s="50"/>
     </row>
     <row r="75" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="113"/>
-      <c r="B75" s="72"/>
-      <c r="C75" s="73"/>
-      <c r="D75" s="161"/>
-      <c r="E75" s="62"/>
-      <c r="F75" s="63"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="52"/>
+      <c r="A75" s="135"/>
+      <c r="B75" s="124"/>
+      <c r="C75" s="125"/>
+      <c r="D75" s="63"/>
+      <c r="E75" s="60"/>
+      <c r="F75" s="128"/>
+      <c r="G75" s="121"/>
+      <c r="H75" s="50"/>
     </row>
     <row r="76" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="65"/>
-      <c r="B76" s="72"/>
-      <c r="C76" s="73"/>
-      <c r="D76" s="161"/>
-      <c r="E76" s="62"/>
-      <c r="F76" s="76"/>
-      <c r="G76" s="74"/>
-      <c r="H76" s="52"/>
+      <c r="A76" s="123"/>
+      <c r="B76" s="124"/>
+      <c r="C76" s="125"/>
+      <c r="D76" s="63"/>
+      <c r="E76" s="60"/>
+      <c r="F76" s="79"/>
+      <c r="G76" s="121"/>
+      <c r="H76" s="50"/>
     </row>
     <row r="77" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="65"/>
-      <c r="B77" s="72"/>
-      <c r="C77" s="73"/>
-      <c r="D77" s="161"/>
-      <c r="E77" s="62"/>
-      <c r="F77" s="63"/>
-      <c r="G77" s="74"/>
-      <c r="H77" s="52"/>
+      <c r="A77" s="123"/>
+      <c r="B77" s="124"/>
+      <c r="C77" s="125"/>
+      <c r="D77" s="63"/>
+      <c r="E77" s="60"/>
+      <c r="F77" s="128"/>
+      <c r="G77" s="121"/>
+      <c r="H77" s="50"/>
     </row>
     <row r="78" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="65"/>
-      <c r="B78" s="72"/>
-      <c r="C78" s="73"/>
-      <c r="D78" s="161"/>
-      <c r="E78" s="62"/>
-      <c r="F78" s="63"/>
-      <c r="G78" s="74"/>
-      <c r="H78" s="52"/>
+      <c r="A78" s="123"/>
+      <c r="B78" s="124"/>
+      <c r="C78" s="125"/>
+      <c r="D78" s="63"/>
+      <c r="E78" s="60"/>
+      <c r="F78" s="128"/>
+      <c r="G78" s="121"/>
+      <c r="H78" s="50"/>
     </row>
     <row r="79" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="65"/>
-      <c r="B79" s="72"/>
-      <c r="C79" s="73"/>
-      <c r="D79" s="161"/>
-      <c r="E79" s="62"/>
-      <c r="F79" s="63"/>
-      <c r="G79" s="74"/>
-      <c r="H79" s="52"/>
+      <c r="A79" s="123"/>
+      <c r="B79" s="124"/>
+      <c r="C79" s="125"/>
+      <c r="D79" s="63"/>
+      <c r="E79" s="60"/>
+      <c r="F79" s="128"/>
+      <c r="G79" s="121"/>
+      <c r="H79" s="50"/>
     </row>
     <row r="80" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="80" t="s">
+      <c r="A80" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="B80" s="71"/>
-      <c r="C80" s="69"/>
-      <c r="D80" s="55">
+      <c r="B80" s="67"/>
+      <c r="C80" s="70"/>
+      <c r="D80" s="53">
         <f>SUM(D70:D79)</f>
         <v>0</v>
       </c>
-      <c r="E80" s="56">
+      <c r="E80" s="54">
         <f>SUM(E70:E79)</f>
         <v>0</v>
       </c>
-      <c r="F80" s="83"/>
-      <c r="G80" s="69"/>
-      <c r="H80" s="31"/>
+      <c r="F80" s="134"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="29"/>
     </row>
     <row r="81" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="97"/>
-      <c r="B81" s="98"/>
-      <c r="C81" s="98"/>
-      <c r="D81" s="98"/>
-      <c r="E81" s="98"/>
-      <c r="F81" s="98"/>
-      <c r="G81" s="98"/>
-      <c r="H81" s="99"/>
+      <c r="A81" s="141"/>
+      <c r="B81" s="114"/>
+      <c r="C81" s="114"/>
+      <c r="D81" s="114"/>
+      <c r="E81" s="114"/>
+      <c r="F81" s="114"/>
+      <c r="G81" s="114"/>
+      <c r="H81" s="115"/>
     </row>
     <row r="82" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="100" t="s">
+      <c r="A82" s="142" t="s">
         <v>31</v>
       </c>
-      <c r="B82" s="71"/>
-      <c r="C82" s="69"/>
-      <c r="D82" s="101">
+      <c r="B82" s="67"/>
+      <c r="C82" s="70"/>
+      <c r="D82" s="143">
         <f>SUM(F25,D40,D65,D80,D49)</f>
         <v>0</v>
       </c>
-      <c r="E82" s="71"/>
-      <c r="F82" s="69"/>
-      <c r="G82" s="102"/>
-      <c r="H82" s="99"/>
+      <c r="E82" s="67"/>
+      <c r="F82" s="70"/>
+      <c r="G82" s="144"/>
+      <c r="H82" s="115"/>
     </row>
     <row r="83" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="103" t="s">
+      <c r="A83" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="B83" s="98"/>
-      <c r="C83" s="98"/>
-      <c r="D83" s="98"/>
-      <c r="E83" s="98"/>
-      <c r="F83" s="98"/>
-      <c r="G83" s="98"/>
-      <c r="H83" s="99"/>
+      <c r="B83" s="114"/>
+      <c r="C83" s="114"/>
+      <c r="D83" s="114"/>
+      <c r="E83" s="114"/>
+      <c r="F83" s="114"/>
+      <c r="G83" s="114"/>
+      <c r="H83" s="115"/>
     </row>
     <row r="84" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="37" t="s">
+      <c r="A84" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="B84" s="104"/>
-      <c r="C84" s="90"/>
-      <c r="D84" s="90"/>
-      <c r="E84" s="105" t="s">
+      <c r="B84" s="146"/>
+      <c r="C84" s="117"/>
+      <c r="D84" s="117"/>
+      <c r="E84" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="F84" s="98"/>
-      <c r="G84" s="106"/>
-      <c r="H84" s="91"/>
+      <c r="F84" s="114"/>
+      <c r="G84" s="148"/>
+      <c r="H84" s="118"/>
     </row>
     <row r="85" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="40" t="s">
+      <c r="A85" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="B85" s="107"/>
-      <c r="C85" s="98"/>
-      <c r="D85" s="41"/>
-      <c r="E85" s="108" t="s">
+      <c r="B85" s="149"/>
+      <c r="C85" s="114"/>
+      <c r="D85" s="39"/>
+      <c r="E85" s="150" t="s">
         <v>34</v>
       </c>
-      <c r="F85" s="98"/>
-      <c r="G85" s="109"/>
-      <c r="H85" s="86"/>
+      <c r="F85" s="114"/>
+      <c r="G85" s="151"/>
+      <c r="H85" s="110"/>
     </row>
     <row r="86" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="40"/>
-      <c r="B86" s="110" t="s">
+      <c r="A86" s="38"/>
+      <c r="B86" s="152" t="s">
         <v>35</v>
       </c>
-      <c r="C86" s="98"/>
-      <c r="D86" s="41"/>
-      <c r="E86" s="44"/>
-      <c r="F86" s="45"/>
-      <c r="G86" s="111" t="s">
+      <c r="C86" s="114"/>
+      <c r="D86" s="39"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="43"/>
+      <c r="G86" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="H86" s="99"/>
+      <c r="H86" s="115"/>
     </row>
     <row r="87" spans="1:8" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="40"/>
-      <c r="B87" s="43"/>
-      <c r="C87" s="41"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="44"/>
-      <c r="F87" s="45"/>
-      <c r="G87" s="44"/>
+      <c r="A87" s="38"/>
+      <c r="B87" s="41"/>
+      <c r="C87" s="39"/>
+      <c r="D87" s="39"/>
+      <c r="E87" s="42"/>
+      <c r="F87" s="43"/>
+      <c r="G87" s="42"/>
       <c r="H87" s="5"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="40"/>
-      <c r="B88" s="43"/>
-      <c r="C88" s="41"/>
-      <c r="D88" s="41"/>
-      <c r="E88" s="44"/>
-      <c r="F88" s="45"/>
-      <c r="G88" s="44"/>
+      <c r="A88" s="38"/>
+      <c r="B88" s="41"/>
+      <c r="C88" s="39"/>
+      <c r="D88" s="39"/>
+      <c r="E88" s="42"/>
+      <c r="F88" s="43"/>
+      <c r="G88" s="42"/>
       <c r="H88" s="5"/>
     </row>
     <row r="89" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="40"/>
-      <c r="B89" s="45"/>
-      <c r="C89" s="39" t="s">
+      <c r="A89" s="38"/>
+      <c r="B89" s="43"/>
+      <c r="C89" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="D89" s="38"/>
-      <c r="E89" s="38"/>
-      <c r="F89" s="38"/>
-      <c r="G89" s="45"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+      <c r="G89" s="43"/>
       <c r="H89" s="5"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="40"/>
-      <c r="B90" s="45"/>
-      <c r="C90" s="42" t="s">
+      <c r="A90" s="38"/>
+      <c r="B90" s="43"/>
+      <c r="C90" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="D90" s="46"/>
-      <c r="E90" s="46"/>
-      <c r="F90" s="46"/>
-      <c r="G90" s="45"/>
+      <c r="D90" s="44"/>
+      <c r="E90" s="44"/>
+      <c r="F90" s="44"/>
+      <c r="G90" s="43"/>
       <c r="H90" s="5"/>
     </row>
     <row r="91" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="40"/>
-      <c r="B91" s="45"/>
-      <c r="C91" s="41"/>
-      <c r="D91" s="110" t="s">
+      <c r="A91" s="38"/>
+      <c r="B91" s="43"/>
+      <c r="C91" s="39"/>
+      <c r="D91" s="152" t="s">
         <v>37</v>
       </c>
-      <c r="E91" s="98"/>
-      <c r="F91" s="98"/>
-      <c r="G91" s="45"/>
+      <c r="E91" s="114"/>
+      <c r="F91" s="114"/>
+      <c r="G91" s="43"/>
       <c r="H91" s="5"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="15"/>
-      <c r="B92" s="16"/>
-      <c r="C92" s="16"/>
+      <c r="A92" s="13"/>
+      <c r="B92" s="14"/>
+      <c r="C92" s="14"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
-      <c r="F92" s="16"/>
-      <c r="G92" s="16"/>
-      <c r="H92" s="17"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="15"/>
     </row>
     <row r="93" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="112" t="s">
+      <c r="A93" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="B93" s="71"/>
-      <c r="C93" s="71"/>
-      <c r="D93" s="71"/>
-      <c r="E93" s="71"/>
-      <c r="F93" s="71"/>
-      <c r="G93" s="71"/>
-      <c r="H93" s="88"/>
+      <c r="B93" s="67"/>
+      <c r="C93" s="67"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="67"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="67"/>
+      <c r="H93" s="112"/>
     </row>
     <row r="94" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="94" t="s">
+      <c r="A94" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="B94" s="95"/>
-      <c r="C94" s="95"/>
-      <c r="D94" s="95"/>
-      <c r="E94" s="95"/>
-      <c r="F94" s="95"/>
-      <c r="G94" s="95"/>
-      <c r="H94" s="96"/>
+      <c r="B94" s="139"/>
+      <c r="C94" s="139"/>
+      <c r="D94" s="139"/>
+      <c r="E94" s="139"/>
+      <c r="F94" s="139"/>
+      <c r="G94" s="139"/>
+      <c r="H94" s="140"/>
     </row>
     <row r="95" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="16"/>
-      <c r="B95" s="16"/>
-      <c r="C95" s="16"/>
+      <c r="A95" s="14"/>
+      <c r="B95" s="14"/>
+      <c r="C95" s="14"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
-      <c r="F95" s="16"/>
-      <c r="G95" s="16"/>
-      <c r="H95" s="45"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="14"/>
+      <c r="H95" s="43"/>
     </row>
     <row r="96" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="16"/>
-      <c r="B96" s="16"/>
-      <c r="C96" s="16"/>
+      <c r="A96" s="14"/>
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
-      <c r="F96" s="16"/>
-      <c r="G96" s="16"/>
-      <c r="H96" s="45"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="43"/>
     </row>
     <row r="97" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="16"/>
-      <c r="B97" s="16"/>
-      <c r="C97" s="16"/>
+      <c r="A97" s="14"/>
+      <c r="B97" s="14"/>
+      <c r="C97" s="14"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
-      <c r="F97" s="16"/>
-      <c r="G97" s="16"/>
-      <c r="H97" s="45"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="43"/>
     </row>
     <row r="98" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="16"/>
-      <c r="B98" s="16"/>
-      <c r="C98" s="16"/>
+      <c r="A98" s="14"/>
+      <c r="B98" s="14"/>
+      <c r="C98" s="14"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
-      <c r="F98" s="16"/>
-      <c r="G98" s="16"/>
-      <c r="H98" s="45"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="14"/>
+      <c r="H98" s="43"/>
     </row>
     <row r="99" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="16"/>
-      <c r="B99" s="16"/>
-      <c r="C99" s="16"/>
+      <c r="A99" s="14"/>
+      <c r="B99" s="14"/>
+      <c r="C99" s="14"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
-      <c r="F99" s="16"/>
-      <c r="G99" s="16"/>
-      <c r="H99" s="45"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
+      <c r="H99" s="43"/>
     </row>
     <row r="100" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="16"/>
-      <c r="B100" s="16"/>
-      <c r="C100" s="16"/>
+      <c r="A100" s="14"/>
+      <c r="B100" s="14"/>
+      <c r="C100" s="14"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
-      <c r="F100" s="16"/>
-      <c r="G100" s="16"/>
-      <c r="H100" s="45"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="14"/>
+      <c r="H100" s="43"/>
     </row>
     <row r="101" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="16"/>
-      <c r="B101" s="16"/>
-      <c r="C101" s="16"/>
+      <c r="A101" s="14"/>
+      <c r="B101" s="14"/>
+      <c r="C101" s="14"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
-      <c r="F101" s="16"/>
-      <c r="G101" s="16"/>
-      <c r="H101" s="45"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="43"/>
     </row>
     <row r="102" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="16"/>
-      <c r="B102" s="16"/>
-      <c r="C102" s="16"/>
+      <c r="A102" s="14"/>
+      <c r="B102" s="14"/>
+      <c r="C102" s="14"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
-      <c r="F102" s="16"/>
-      <c r="G102" s="16"/>
-      <c r="H102" s="45"/>
+      <c r="F102" s="14"/>
+      <c r="G102" s="14"/>
+      <c r="H102" s="43"/>
     </row>
     <row r="103" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="16"/>
-      <c r="B103" s="16"/>
-      <c r="C103" s="16"/>
+      <c r="A103" s="14"/>
+      <c r="B103" s="14"/>
+      <c r="C103" s="14"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
-      <c r="F103" s="16"/>
-      <c r="G103" s="16"/>
-      <c r="H103" s="45"/>
+      <c r="F103" s="14"/>
+      <c r="G103" s="14"/>
+      <c r="H103" s="43"/>
     </row>
     <row r="104" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="16"/>
-      <c r="B104" s="16"/>
-      <c r="C104" s="16"/>
+      <c r="A104" s="14"/>
+      <c r="B104" s="14"/>
+      <c r="C104" s="14"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
-      <c r="F104" s="16"/>
-      <c r="G104" s="16"/>
-      <c r="H104" s="45"/>
+      <c r="F104" s="14"/>
+      <c r="G104" s="14"/>
+      <c r="H104" s="43"/>
     </row>
     <row r="105" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="16"/>
-      <c r="B105" s="16"/>
-      <c r="C105" s="16"/>
+      <c r="A105" s="14"/>
+      <c r="B105" s="14"/>
+      <c r="C105" s="14"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
-      <c r="F105" s="16"/>
-      <c r="G105" s="16"/>
-      <c r="H105" s="45"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="14"/>
+      <c r="H105" s="43"/>
     </row>
     <row r="106" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="16"/>
-      <c r="B106" s="16"/>
-      <c r="C106" s="16"/>
+      <c r="A106" s="14"/>
+      <c r="B106" s="14"/>
+      <c r="C106" s="14"/>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
-      <c r="F106" s="16"/>
-      <c r="G106" s="16"/>
-      <c r="H106" s="45"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
+      <c r="H106" s="43"/>
     </row>
     <row r="107" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="16"/>
-      <c r="B107" s="16"/>
-      <c r="C107" s="16"/>
+      <c r="A107" s="14"/>
+      <c r="B107" s="14"/>
+      <c r="C107" s="14"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
-      <c r="F107" s="16"/>
-      <c r="G107" s="16"/>
-      <c r="H107" s="45"/>
+      <c r="F107" s="14"/>
+      <c r="G107" s="14"/>
+      <c r="H107" s="43"/>
     </row>
     <row r="108" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="16"/>
-      <c r="B108" s="16"/>
-      <c r="C108" s="16"/>
+      <c r="A108" s="14"/>
+      <c r="B108" s="14"/>
+      <c r="C108" s="14"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
-      <c r="F108" s="16"/>
-      <c r="G108" s="16"/>
-      <c r="H108" s="45"/>
+      <c r="F108" s="14"/>
+      <c r="G108" s="14"/>
+      <c r="H108" s="43"/>
     </row>
     <row r="109" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="16"/>
-      <c r="B109" s="16"/>
-      <c r="C109" s="16"/>
+      <c r="A109" s="14"/>
+      <c r="B109" s="14"/>
+      <c r="C109" s="14"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
-      <c r="F109" s="16"/>
-      <c r="G109" s="16"/>
-      <c r="H109" s="45"/>
+      <c r="F109" s="14"/>
+      <c r="G109" s="14"/>
+      <c r="H109" s="43"/>
     </row>
     <row r="110" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="16"/>
-      <c r="B110" s="16"/>
-      <c r="C110" s="16"/>
+      <c r="A110" s="14"/>
+      <c r="B110" s="14"/>
+      <c r="C110" s="14"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
-      <c r="F110" s="16"/>
-      <c r="G110" s="16"/>
-      <c r="H110" s="45"/>
+      <c r="F110" s="14"/>
+      <c r="G110" s="14"/>
+      <c r="H110" s="43"/>
     </row>
     <row r="111" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="16"/>
-      <c r="B111" s="16"/>
-      <c r="C111" s="16"/>
+      <c r="A111" s="14"/>
+      <c r="B111" s="14"/>
+      <c r="C111" s="14"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
-      <c r="F111" s="16"/>
-      <c r="G111" s="16"/>
-      <c r="H111" s="45"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="14"/>
+      <c r="H111" s="43"/>
     </row>
     <row r="112" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="16"/>
-      <c r="B112" s="16"/>
-      <c r="C112" s="16"/>
+      <c r="A112" s="14"/>
+      <c r="B112" s="14"/>
+      <c r="C112" s="14"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
-      <c r="F112" s="16"/>
-      <c r="G112" s="16"/>
-      <c r="H112" s="45"/>
+      <c r="F112" s="14"/>
+      <c r="G112" s="14"/>
+      <c r="H112" s="43"/>
     </row>
     <row r="113" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="16"/>
-      <c r="B113" s="16"/>
-      <c r="C113" s="16"/>
+      <c r="A113" s="14"/>
+      <c r="B113" s="14"/>
+      <c r="C113" s="14"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
-      <c r="F113" s="16"/>
-      <c r="G113" s="16"/>
-      <c r="H113" s="45"/>
+      <c r="F113" s="14"/>
+      <c r="G113" s="14"/>
+      <c r="H113" s="43"/>
     </row>
     <row r="114" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="16"/>
-      <c r="B114" s="16"/>
-      <c r="C114" s="16"/>
+      <c r="A114" s="14"/>
+      <c r="B114" s="14"/>
+      <c r="C114" s="14"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
-      <c r="F114" s="16"/>
-      <c r="G114" s="16"/>
-      <c r="H114" s="45"/>
+      <c r="F114" s="14"/>
+      <c r="G114" s="14"/>
+      <c r="H114" s="43"/>
     </row>
     <row r="115" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="16"/>
-      <c r="B115" s="16"/>
-      <c r="C115" s="16"/>
+      <c r="A115" s="14"/>
+      <c r="B115" s="14"/>
+      <c r="C115" s="14"/>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
-      <c r="F115" s="16"/>
-      <c r="G115" s="16"/>
-      <c r="H115" s="45"/>
+      <c r="F115" s="14"/>
+      <c r="G115" s="14"/>
+      <c r="H115" s="43"/>
     </row>
     <row r="116" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="16"/>
-      <c r="B116" s="16"/>
-      <c r="C116" s="16"/>
+      <c r="A116" s="14"/>
+      <c r="B116" s="14"/>
+      <c r="C116" s="14"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
-      <c r="F116" s="16"/>
-      <c r="G116" s="16"/>
-      <c r="H116" s="45"/>
+      <c r="F116" s="14"/>
+      <c r="G116" s="14"/>
+      <c r="H116" s="43"/>
     </row>
     <row r="117" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="16"/>
-      <c r="B117" s="16"/>
-      <c r="C117" s="16"/>
+      <c r="A117" s="14"/>
+      <c r="B117" s="14"/>
+      <c r="C117" s="14"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
-      <c r="F117" s="16"/>
-      <c r="G117" s="16"/>
-      <c r="H117" s="45"/>
+      <c r="F117" s="14"/>
+      <c r="G117" s="14"/>
+      <c r="H117" s="43"/>
     </row>
     <row r="118" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="16"/>
-      <c r="B118" s="16"/>
-      <c r="C118" s="16"/>
+      <c r="A118" s="14"/>
+      <c r="B118" s="14"/>
+      <c r="C118" s="14"/>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
-      <c r="F118" s="16"/>
-      <c r="G118" s="16"/>
-      <c r="H118" s="45"/>
+      <c r="F118" s="14"/>
+      <c r="G118" s="14"/>
+      <c r="H118" s="43"/>
     </row>
     <row r="119" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="16"/>
-      <c r="B119" s="16"/>
-      <c r="C119" s="16"/>
+      <c r="A119" s="14"/>
+      <c r="B119" s="14"/>
+      <c r="C119" s="14"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
-      <c r="F119" s="16"/>
-      <c r="G119" s="16"/>
-      <c r="H119" s="45"/>
+      <c r="F119" s="14"/>
+      <c r="G119" s="14"/>
+      <c r="H119" s="43"/>
     </row>
     <row r="120" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="16"/>
-      <c r="B120" s="16"/>
-      <c r="C120" s="16"/>
+      <c r="A120" s="14"/>
+      <c r="B120" s="14"/>
+      <c r="C120" s="14"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
-      <c r="F120" s="16"/>
-      <c r="G120" s="16"/>
-      <c r="H120" s="45"/>
+      <c r="F120" s="14"/>
+      <c r="G120" s="14"/>
+      <c r="H120" s="43"/>
     </row>
     <row r="121" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="16"/>
-      <c r="B121" s="16"/>
-      <c r="C121" s="16"/>
+      <c r="A121" s="14"/>
+      <c r="B121" s="14"/>
+      <c r="C121" s="14"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
-      <c r="F121" s="16"/>
-      <c r="G121" s="16"/>
-      <c r="H121" s="45"/>
+      <c r="F121" s="14"/>
+      <c r="G121" s="14"/>
+      <c r="H121" s="43"/>
     </row>
     <row r="122" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="16"/>
-      <c r="B122" s="16"/>
-      <c r="C122" s="16"/>
+      <c r="A122" s="14"/>
+      <c r="B122" s="14"/>
+      <c r="C122" s="14"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
-      <c r="F122" s="16"/>
-      <c r="G122" s="16"/>
-      <c r="H122" s="45"/>
+      <c r="F122" s="14"/>
+      <c r="G122" s="14"/>
+      <c r="H122" s="43"/>
     </row>
     <row r="123" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="16"/>
-      <c r="B123" s="16"/>
-      <c r="C123" s="16"/>
+      <c r="A123" s="14"/>
+      <c r="B123" s="14"/>
+      <c r="C123" s="14"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
-      <c r="F123" s="16"/>
-      <c r="G123" s="16"/>
-      <c r="H123" s="45"/>
+      <c r="F123" s="14"/>
+      <c r="G123" s="14"/>
+      <c r="H123" s="43"/>
     </row>
     <row r="124" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="16"/>
-      <c r="B124" s="16"/>
-      <c r="C124" s="16"/>
+      <c r="A124" s="14"/>
+      <c r="B124" s="14"/>
+      <c r="C124" s="14"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
-      <c r="F124" s="16"/>
-      <c r="G124" s="16"/>
-      <c r="H124" s="45"/>
+      <c r="F124" s="14"/>
+      <c r="G124" s="14"/>
+      <c r="H124" s="43"/>
     </row>
     <row r="125" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="16"/>
-      <c r="B125" s="16"/>
-      <c r="C125" s="16"/>
+      <c r="A125" s="14"/>
+      <c r="B125" s="14"/>
+      <c r="C125" s="14"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
-      <c r="F125" s="16"/>
-      <c r="G125" s="16"/>
-      <c r="H125" s="45"/>
+      <c r="F125" s="14"/>
+      <c r="G125" s="14"/>
+      <c r="H125" s="43"/>
     </row>
     <row r="126" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="16"/>
-      <c r="B126" s="16"/>
-      <c r="C126" s="16"/>
+      <c r="A126" s="14"/>
+      <c r="B126" s="14"/>
+      <c r="C126" s="14"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
-      <c r="F126" s="16"/>
-      <c r="G126" s="16"/>
-      <c r="H126" s="45"/>
+      <c r="F126" s="14"/>
+      <c r="G126" s="14"/>
+      <c r="H126" s="43"/>
     </row>
     <row r="127" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="16"/>
-      <c r="B127" s="16"/>
-      <c r="C127" s="16"/>
+      <c r="A127" s="14"/>
+      <c r="B127" s="14"/>
+      <c r="C127" s="14"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
-      <c r="F127" s="16"/>
-      <c r="G127" s="16"/>
-      <c r="H127" s="45"/>
+      <c r="F127" s="14"/>
+      <c r="G127" s="14"/>
+      <c r="H127" s="43"/>
     </row>
     <row r="128" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="16"/>
-      <c r="B128" s="16"/>
-      <c r="C128" s="16"/>
+      <c r="A128" s="14"/>
+      <c r="B128" s="14"/>
+      <c r="C128" s="14"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
-      <c r="F128" s="16"/>
-      <c r="G128" s="16"/>
-      <c r="H128" s="45"/>
+      <c r="F128" s="14"/>
+      <c r="G128" s="14"/>
+      <c r="H128" s="43"/>
     </row>
     <row r="129" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="16"/>
-      <c r="B129" s="16"/>
-      <c r="C129" s="16"/>
+      <c r="A129" s="14"/>
+      <c r="B129" s="14"/>
+      <c r="C129" s="14"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
-      <c r="F129" s="16"/>
-      <c r="G129" s="16"/>
-      <c r="H129" s="45"/>
+      <c r="F129" s="14"/>
+      <c r="G129" s="14"/>
+      <c r="H129" s="43"/>
     </row>
     <row r="130" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="16"/>
-      <c r="B130" s="16"/>
-      <c r="C130" s="16"/>
+      <c r="A130" s="14"/>
+      <c r="B130" s="14"/>
+      <c r="C130" s="14"/>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
-      <c r="F130" s="16"/>
-      <c r="G130" s="16"/>
-      <c r="H130" s="45"/>
+      <c r="F130" s="14"/>
+      <c r="G130" s="14"/>
+      <c r="H130" s="43"/>
     </row>
     <row r="131" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="16"/>
-      <c r="B131" s="16"/>
-      <c r="C131" s="16"/>
+      <c r="A131" s="14"/>
+      <c r="B131" s="14"/>
+      <c r="C131" s="14"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
-      <c r="F131" s="16"/>
-      <c r="G131" s="16"/>
-      <c r="H131" s="45"/>
+      <c r="F131" s="14"/>
+      <c r="G131" s="14"/>
+      <c r="H131" s="43"/>
     </row>
     <row r="132" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="16"/>
-      <c r="B132" s="16"/>
-      <c r="C132" s="16"/>
+      <c r="A132" s="14"/>
+      <c r="B132" s="14"/>
+      <c r="C132" s="14"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
-      <c r="F132" s="16"/>
-      <c r="G132" s="16"/>
-      <c r="H132" s="45"/>
+      <c r="F132" s="14"/>
+      <c r="G132" s="14"/>
+      <c r="H132" s="43"/>
     </row>
     <row r="133" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="16"/>
-      <c r="B133" s="16"/>
-      <c r="C133" s="16"/>
+      <c r="A133" s="14"/>
+      <c r="B133" s="14"/>
+      <c r="C133" s="14"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
-      <c r="F133" s="16"/>
-      <c r="G133" s="16"/>
-      <c r="H133" s="45"/>
+      <c r="F133" s="14"/>
+      <c r="G133" s="14"/>
+      <c r="H133" s="43"/>
     </row>
     <row r="134" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="16"/>
-      <c r="B134" s="16"/>
-      <c r="C134" s="16"/>
+      <c r="A134" s="14"/>
+      <c r="B134" s="14"/>
+      <c r="C134" s="14"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
-      <c r="F134" s="16"/>
-      <c r="G134" s="16"/>
-      <c r="H134" s="45"/>
+      <c r="F134" s="14"/>
+      <c r="G134" s="14"/>
+      <c r="H134" s="43"/>
     </row>
     <row r="135" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="16"/>
-      <c r="B135" s="16"/>
-      <c r="C135" s="16"/>
+      <c r="A135" s="14"/>
+      <c r="B135" s="14"/>
+      <c r="C135" s="14"/>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
-      <c r="F135" s="16"/>
-      <c r="G135" s="16"/>
-      <c r="H135" s="45"/>
+      <c r="F135" s="14"/>
+      <c r="G135" s="14"/>
+      <c r="H135" s="43"/>
     </row>
     <row r="136" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="16"/>
-      <c r="B136" s="16"/>
-      <c r="C136" s="16"/>
+      <c r="A136" s="14"/>
+      <c r="B136" s="14"/>
+      <c r="C136" s="14"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
-      <c r="F136" s="16"/>
-      <c r="G136" s="16"/>
-      <c r="H136" s="45"/>
+      <c r="F136" s="14"/>
+      <c r="G136" s="14"/>
+      <c r="H136" s="43"/>
     </row>
     <row r="137" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="16"/>
-      <c r="B137" s="16"/>
-      <c r="C137" s="16"/>
+      <c r="A137" s="14"/>
+      <c r="B137" s="14"/>
+      <c r="C137" s="14"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
-      <c r="F137" s="16"/>
-      <c r="G137" s="16"/>
-      <c r="H137" s="45"/>
+      <c r="F137" s="14"/>
+      <c r="G137" s="14"/>
+      <c r="H137" s="43"/>
     </row>
     <row r="138" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="16"/>
-      <c r="B138" s="16"/>
-      <c r="C138" s="16"/>
+      <c r="A138" s="14"/>
+      <c r="B138" s="14"/>
+      <c r="C138" s="14"/>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
-      <c r="F138" s="16"/>
-      <c r="G138" s="16"/>
-      <c r="H138" s="45"/>
+      <c r="F138" s="14"/>
+      <c r="G138" s="14"/>
+      <c r="H138" s="43"/>
     </row>
     <row r="139" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="16"/>
-      <c r="B139" s="16"/>
-      <c r="C139" s="16"/>
+      <c r="A139" s="14"/>
+      <c r="B139" s="14"/>
+      <c r="C139" s="14"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
-      <c r="F139" s="16"/>
-      <c r="G139" s="16"/>
-      <c r="H139" s="45"/>
+      <c r="F139" s="14"/>
+      <c r="G139" s="14"/>
+      <c r="H139" s="43"/>
     </row>
     <row r="140" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="16"/>
-      <c r="B140" s="16"/>
-      <c r="C140" s="16"/>
+      <c r="A140" s="14"/>
+      <c r="B140" s="14"/>
+      <c r="C140" s="14"/>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
-      <c r="F140" s="16"/>
-      <c r="G140" s="16"/>
-      <c r="H140" s="45"/>
+      <c r="F140" s="14"/>
+      <c r="G140" s="14"/>
+      <c r="H140" s="43"/>
     </row>
     <row r="141" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="16"/>
-      <c r="B141" s="16"/>
-      <c r="C141" s="16"/>
+      <c r="A141" s="14"/>
+      <c r="B141" s="14"/>
+      <c r="C141" s="14"/>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
-      <c r="F141" s="16"/>
-      <c r="G141" s="16"/>
-      <c r="H141" s="45"/>
+      <c r="F141" s="14"/>
+      <c r="G141" s="14"/>
+      <c r="H141" s="43"/>
     </row>
     <row r="142" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="16"/>
-      <c r="B142" s="16"/>
-      <c r="C142" s="16"/>
+      <c r="A142" s="14"/>
+      <c r="B142" s="14"/>
+      <c r="C142" s="14"/>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
-      <c r="F142" s="16"/>
-      <c r="G142" s="16"/>
-      <c r="H142" s="45"/>
+      <c r="F142" s="14"/>
+      <c r="G142" s="14"/>
+      <c r="H142" s="43"/>
     </row>
     <row r="143" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="16"/>
-      <c r="B143" s="16"/>
-      <c r="C143" s="16"/>
+      <c r="A143" s="14"/>
+      <c r="B143" s="14"/>
+      <c r="C143" s="14"/>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
-      <c r="F143" s="16"/>
-      <c r="G143" s="16"/>
-      <c r="H143" s="45"/>
+      <c r="F143" s="14"/>
+      <c r="G143" s="14"/>
+      <c r="H143" s="43"/>
     </row>
     <row r="144" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="16"/>
-      <c r="B144" s="16"/>
-      <c r="C144" s="16"/>
+      <c r="A144" s="14"/>
+      <c r="B144" s="14"/>
+      <c r="C144" s="14"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
-      <c r="F144" s="16"/>
-      <c r="G144" s="16"/>
-      <c r="H144" s="45"/>
+      <c r="F144" s="14"/>
+      <c r="G144" s="14"/>
+      <c r="H144" s="43"/>
     </row>
     <row r="145" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="16"/>
-      <c r="B145" s="16"/>
-      <c r="C145" s="16"/>
+      <c r="A145" s="14"/>
+      <c r="B145" s="14"/>
+      <c r="C145" s="14"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
-      <c r="F145" s="16"/>
-      <c r="G145" s="16"/>
-      <c r="H145" s="45"/>
+      <c r="F145" s="14"/>
+      <c r="G145" s="14"/>
+      <c r="H145" s="43"/>
     </row>
     <row r="146" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="16"/>
-      <c r="B146" s="16"/>
-      <c r="C146" s="16"/>
+      <c r="A146" s="14"/>
+      <c r="B146" s="14"/>
+      <c r="C146" s="14"/>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
-      <c r="F146" s="16"/>
-      <c r="G146" s="16"/>
-      <c r="H146" s="45"/>
+      <c r="F146" s="14"/>
+      <c r="G146" s="14"/>
+      <c r="H146" s="43"/>
     </row>
     <row r="147" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="16"/>
-      <c r="B147" s="16"/>
-      <c r="C147" s="16"/>
+      <c r="A147" s="14"/>
+      <c r="B147" s="14"/>
+      <c r="C147" s="14"/>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
-      <c r="F147" s="16"/>
-      <c r="G147" s="16"/>
-      <c r="H147" s="45"/>
+      <c r="F147" s="14"/>
+      <c r="G147" s="14"/>
+      <c r="H147" s="43"/>
     </row>
     <row r="148" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="16"/>
-      <c r="B148" s="16"/>
-      <c r="C148" s="16"/>
+      <c r="A148" s="14"/>
+      <c r="B148" s="14"/>
+      <c r="C148" s="14"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
-      <c r="F148" s="16"/>
-      <c r="G148" s="16"/>
-      <c r="H148" s="45"/>
+      <c r="F148" s="14"/>
+      <c r="G148" s="14"/>
+      <c r="H148" s="43"/>
     </row>
     <row r="149" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="16"/>
-      <c r="B149" s="16"/>
-      <c r="C149" s="16"/>
+      <c r="A149" s="14"/>
+      <c r="B149" s="14"/>
+      <c r="C149" s="14"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
-      <c r="F149" s="16"/>
-      <c r="G149" s="16"/>
-      <c r="H149" s="45"/>
+      <c r="F149" s="14"/>
+      <c r="G149" s="14"/>
+      <c r="H149" s="43"/>
     </row>
     <row r="150" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="16"/>
-      <c r="B150" s="16"/>
-      <c r="C150" s="16"/>
+      <c r="A150" s="14"/>
+      <c r="B150" s="14"/>
+      <c r="C150" s="14"/>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
-      <c r="F150" s="16"/>
-      <c r="G150" s="16"/>
-      <c r="H150" s="45"/>
+      <c r="F150" s="14"/>
+      <c r="G150" s="14"/>
+      <c r="H150" s="43"/>
     </row>
     <row r="151" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="16"/>
-      <c r="B151" s="16"/>
-      <c r="C151" s="16"/>
+      <c r="A151" s="14"/>
+      <c r="B151" s="14"/>
+      <c r="C151" s="14"/>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
-      <c r="F151" s="16"/>
-      <c r="G151" s="16"/>
-      <c r="H151" s="45"/>
+      <c r="F151" s="14"/>
+      <c r="G151" s="14"/>
+      <c r="H151" s="43"/>
     </row>
     <row r="152" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="16"/>
-      <c r="B152" s="16"/>
-      <c r="C152" s="16"/>
+      <c r="A152" s="14"/>
+      <c r="B152" s="14"/>
+      <c r="C152" s="14"/>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
-      <c r="F152" s="16"/>
-      <c r="G152" s="16"/>
-      <c r="H152" s="45"/>
+      <c r="F152" s="14"/>
+      <c r="G152" s="14"/>
+      <c r="H152" s="43"/>
     </row>
     <row r="153" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="16"/>
-      <c r="B153" s="16"/>
-      <c r="C153" s="16"/>
+      <c r="A153" s="14"/>
+      <c r="B153" s="14"/>
+      <c r="C153" s="14"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
-      <c r="F153" s="16"/>
-      <c r="G153" s="16"/>
-      <c r="H153" s="45"/>
+      <c r="F153" s="14"/>
+      <c r="G153" s="14"/>
+      <c r="H153" s="43"/>
     </row>
     <row r="154" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="16"/>
-      <c r="B154" s="16"/>
-      <c r="C154" s="16"/>
+      <c r="A154" s="14"/>
+      <c r="B154" s="14"/>
+      <c r="C154" s="14"/>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
-      <c r="F154" s="16"/>
-      <c r="G154" s="16"/>
-      <c r="H154" s="45"/>
+      <c r="F154" s="14"/>
+      <c r="G154" s="14"/>
+      <c r="H154" s="43"/>
     </row>
     <row r="155" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="16"/>
-      <c r="B155" s="16"/>
-      <c r="C155" s="16"/>
+      <c r="A155" s="14"/>
+      <c r="B155" s="14"/>
+      <c r="C155" s="14"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
-      <c r="F155" s="16"/>
-      <c r="G155" s="16"/>
-      <c r="H155" s="45"/>
+      <c r="F155" s="14"/>
+      <c r="G155" s="14"/>
+      <c r="H155" s="43"/>
     </row>
     <row r="156" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="16"/>
-      <c r="B156" s="16"/>
-      <c r="C156" s="16"/>
+      <c r="A156" s="14"/>
+      <c r="B156" s="14"/>
+      <c r="C156" s="14"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
-      <c r="F156" s="16"/>
-      <c r="G156" s="16"/>
-      <c r="H156" s="45"/>
+      <c r="F156" s="14"/>
+      <c r="G156" s="14"/>
+      <c r="H156" s="43"/>
     </row>
     <row r="157" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="16"/>
-      <c r="B157" s="16"/>
-      <c r="C157" s="16"/>
+      <c r="A157" s="14"/>
+      <c r="B157" s="14"/>
+      <c r="C157" s="14"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
-      <c r="F157" s="16"/>
-      <c r="G157" s="16"/>
-      <c r="H157" s="45"/>
+      <c r="F157" s="14"/>
+      <c r="G157" s="14"/>
+      <c r="H157" s="43"/>
     </row>
     <row r="158" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="16"/>
-      <c r="B158" s="16"/>
-      <c r="C158" s="16"/>
+      <c r="A158" s="14"/>
+      <c r="B158" s="14"/>
+      <c r="C158" s="14"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
-      <c r="F158" s="16"/>
-      <c r="G158" s="16"/>
-      <c r="H158" s="45"/>
+      <c r="F158" s="14"/>
+      <c r="G158" s="14"/>
+      <c r="H158" s="43"/>
     </row>
     <row r="159" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="16"/>
-      <c r="B159" s="16"/>
-      <c r="C159" s="16"/>
+      <c r="A159" s="14"/>
+      <c r="B159" s="14"/>
+      <c r="C159" s="14"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
-      <c r="F159" s="16"/>
-      <c r="G159" s="16"/>
-      <c r="H159" s="45"/>
+      <c r="F159" s="14"/>
+      <c r="G159" s="14"/>
+      <c r="H159" s="43"/>
     </row>
     <row r="160" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="16"/>
-      <c r="B160" s="16"/>
-      <c r="C160" s="16"/>
+      <c r="A160" s="14"/>
+      <c r="B160" s="14"/>
+      <c r="C160" s="14"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
-      <c r="F160" s="16"/>
-      <c r="G160" s="16"/>
-      <c r="H160" s="45"/>
+      <c r="F160" s="14"/>
+      <c r="G160" s="14"/>
+      <c r="H160" s="43"/>
     </row>
     <row r="161" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="16"/>
-      <c r="B161" s="16"/>
-      <c r="C161" s="16"/>
+      <c r="A161" s="14"/>
+      <c r="B161" s="14"/>
+      <c r="C161" s="14"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
-      <c r="F161" s="16"/>
-      <c r="G161" s="16"/>
-      <c r="H161" s="45"/>
+      <c r="F161" s="14"/>
+      <c r="G161" s="14"/>
+      <c r="H161" s="43"/>
     </row>
     <row r="162" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="16"/>
-      <c r="B162" s="16"/>
-      <c r="C162" s="16"/>
+      <c r="A162" s="14"/>
+      <c r="B162" s="14"/>
+      <c r="C162" s="14"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
-      <c r="F162" s="16"/>
-      <c r="G162" s="16"/>
-      <c r="H162" s="45"/>
+      <c r="F162" s="14"/>
+      <c r="G162" s="14"/>
+      <c r="H162" s="43"/>
     </row>
     <row r="163" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="16"/>
-      <c r="B163" s="16"/>
-      <c r="C163" s="16"/>
+      <c r="A163" s="14"/>
+      <c r="B163" s="14"/>
+      <c r="C163" s="14"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
-      <c r="F163" s="16"/>
-      <c r="G163" s="16"/>
-      <c r="H163" s="45"/>
+      <c r="F163" s="14"/>
+      <c r="G163" s="14"/>
+      <c r="H163" s="43"/>
     </row>
     <row r="164" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="16"/>
-      <c r="B164" s="16"/>
-      <c r="C164" s="16"/>
+      <c r="A164" s="14"/>
+      <c r="B164" s="14"/>
+      <c r="C164" s="14"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
-      <c r="F164" s="16"/>
-      <c r="G164" s="16"/>
-      <c r="H164" s="45"/>
+      <c r="F164" s="14"/>
+      <c r="G164" s="14"/>
+      <c r="H164" s="43"/>
     </row>
     <row r="165" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="16"/>
-      <c r="B165" s="16"/>
-      <c r="C165" s="16"/>
+      <c r="A165" s="14"/>
+      <c r="B165" s="14"/>
+      <c r="C165" s="14"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
-      <c r="F165" s="16"/>
-      <c r="G165" s="16"/>
-      <c r="H165" s="45"/>
+      <c r="F165" s="14"/>
+      <c r="G165" s="14"/>
+      <c r="H165" s="43"/>
     </row>
     <row r="166" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="16"/>
-      <c r="B166" s="16"/>
-      <c r="C166" s="16"/>
+      <c r="A166" s="14"/>
+      <c r="B166" s="14"/>
+      <c r="C166" s="14"/>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
-      <c r="F166" s="16"/>
-      <c r="G166" s="16"/>
-      <c r="H166" s="45"/>
+      <c r="F166" s="14"/>
+      <c r="G166" s="14"/>
+      <c r="H166" s="43"/>
     </row>
     <row r="167" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="16"/>
-      <c r="B167" s="16"/>
-      <c r="C167" s="16"/>
+      <c r="A167" s="14"/>
+      <c r="B167" s="14"/>
+      <c r="C167" s="14"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
-      <c r="F167" s="16"/>
-      <c r="G167" s="16"/>
-      <c r="H167" s="45"/>
+      <c r="F167" s="14"/>
+      <c r="G167" s="14"/>
+      <c r="H167" s="43"/>
     </row>
     <row r="168" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="16"/>
-      <c r="B168" s="16"/>
-      <c r="C168" s="16"/>
+      <c r="A168" s="14"/>
+      <c r="B168" s="14"/>
+      <c r="C168" s="14"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
-      <c r="F168" s="16"/>
-      <c r="G168" s="16"/>
-      <c r="H168" s="45"/>
+      <c r="F168" s="14"/>
+      <c r="G168" s="14"/>
+      <c r="H168" s="43"/>
     </row>
     <row r="169" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="16"/>
-      <c r="B169" s="16"/>
-      <c r="C169" s="16"/>
+      <c r="A169" s="14"/>
+      <c r="B169" s="14"/>
+      <c r="C169" s="14"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
-      <c r="F169" s="16"/>
-      <c r="G169" s="16"/>
-      <c r="H169" s="45"/>
+      <c r="F169" s="14"/>
+      <c r="G169" s="14"/>
+      <c r="H169" s="43"/>
     </row>
     <row r="170" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="16"/>
-      <c r="B170" s="16"/>
-      <c r="C170" s="16"/>
+      <c r="A170" s="14"/>
+      <c r="B170" s="14"/>
+      <c r="C170" s="14"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
-      <c r="F170" s="16"/>
-      <c r="G170" s="16"/>
-      <c r="H170" s="45"/>
+      <c r="F170" s="14"/>
+      <c r="G170" s="14"/>
+      <c r="H170" s="43"/>
     </row>
     <row r="171" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="16"/>
-      <c r="B171" s="16"/>
-      <c r="C171" s="16"/>
+      <c r="A171" s="14"/>
+      <c r="B171" s="14"/>
+      <c r="C171" s="14"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
-      <c r="F171" s="16"/>
-      <c r="G171" s="16"/>
-      <c r="H171" s="45"/>
+      <c r="F171" s="14"/>
+      <c r="G171" s="14"/>
+      <c r="H171" s="43"/>
     </row>
     <row r="172" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="16"/>
-      <c r="B172" s="16"/>
-      <c r="C172" s="16"/>
+      <c r="A172" s="14"/>
+      <c r="B172" s="14"/>
+      <c r="C172" s="14"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
-      <c r="F172" s="16"/>
-      <c r="G172" s="16"/>
-      <c r="H172" s="45"/>
+      <c r="F172" s="14"/>
+      <c r="G172" s="14"/>
+      <c r="H172" s="43"/>
     </row>
     <row r="173" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="16"/>
-      <c r="B173" s="16"/>
-      <c r="C173" s="16"/>
+      <c r="A173" s="14"/>
+      <c r="B173" s="14"/>
+      <c r="C173" s="14"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
-      <c r="F173" s="16"/>
-      <c r="G173" s="16"/>
-      <c r="H173" s="45"/>
+      <c r="F173" s="14"/>
+      <c r="G173" s="14"/>
+      <c r="H173" s="43"/>
     </row>
     <row r="174" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="16"/>
-      <c r="B174" s="16"/>
-      <c r="C174" s="16"/>
+      <c r="A174" s="14"/>
+      <c r="B174" s="14"/>
+      <c r="C174" s="14"/>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
-      <c r="F174" s="16"/>
-      <c r="G174" s="16"/>
-      <c r="H174" s="45"/>
+      <c r="F174" s="14"/>
+      <c r="G174" s="14"/>
+      <c r="H174" s="43"/>
     </row>
     <row r="175" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="16"/>
-      <c r="B175" s="16"/>
-      <c r="C175" s="16"/>
+      <c r="A175" s="14"/>
+      <c r="B175" s="14"/>
+      <c r="C175" s="14"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
-      <c r="F175" s="16"/>
-      <c r="G175" s="16"/>
-      <c r="H175" s="45"/>
+      <c r="F175" s="14"/>
+      <c r="G175" s="14"/>
+      <c r="H175" s="43"/>
     </row>
     <row r="176" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="16"/>
-      <c r="B176" s="16"/>
-      <c r="C176" s="16"/>
+      <c r="A176" s="14"/>
+      <c r="B176" s="14"/>
+      <c r="C176" s="14"/>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
-      <c r="F176" s="16"/>
-      <c r="G176" s="16"/>
-      <c r="H176" s="45"/>
+      <c r="F176" s="14"/>
+      <c r="G176" s="14"/>
+      <c r="H176" s="43"/>
     </row>
     <row r="177" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="16"/>
-      <c r="B177" s="16"/>
-      <c r="C177" s="16"/>
+      <c r="A177" s="14"/>
+      <c r="B177" s="14"/>
+      <c r="C177" s="14"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
-      <c r="F177" s="16"/>
-      <c r="G177" s="16"/>
-      <c r="H177" s="45"/>
+      <c r="F177" s="14"/>
+      <c r="G177" s="14"/>
+      <c r="H177" s="43"/>
     </row>
     <row r="178" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="16"/>
-      <c r="B178" s="16"/>
-      <c r="C178" s="16"/>
+      <c r="A178" s="14"/>
+      <c r="B178" s="14"/>
+      <c r="C178" s="14"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
-      <c r="F178" s="16"/>
-      <c r="G178" s="16"/>
-      <c r="H178" s="45"/>
+      <c r="F178" s="14"/>
+      <c r="G178" s="14"/>
+      <c r="H178" s="43"/>
     </row>
     <row r="179" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="16"/>
-      <c r="B179" s="16"/>
-      <c r="C179" s="16"/>
+      <c r="A179" s="14"/>
+      <c r="B179" s="14"/>
+      <c r="C179" s="14"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
-      <c r="F179" s="16"/>
-      <c r="G179" s="16"/>
-      <c r="H179" s="45"/>
+      <c r="F179" s="14"/>
+      <c r="G179" s="14"/>
+      <c r="H179" s="43"/>
     </row>
     <row r="180" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="16"/>
-      <c r="B180" s="16"/>
-      <c r="C180" s="16"/>
+      <c r="A180" s="14"/>
+      <c r="B180" s="14"/>
+      <c r="C180" s="14"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
-      <c r="F180" s="16"/>
-      <c r="G180" s="16"/>
-      <c r="H180" s="45"/>
+      <c r="F180" s="14"/>
+      <c r="G180" s="14"/>
+      <c r="H180" s="43"/>
     </row>
     <row r="181" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="16"/>
-      <c r="B181" s="16"/>
-      <c r="C181" s="16"/>
+      <c r="A181" s="14"/>
+      <c r="B181" s="14"/>
+      <c r="C181" s="14"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
-      <c r="F181" s="16"/>
-      <c r="G181" s="16"/>
-      <c r="H181" s="45"/>
+      <c r="F181" s="14"/>
+      <c r="G181" s="14"/>
+      <c r="H181" s="43"/>
     </row>
     <row r="182" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="16"/>
-      <c r="B182" s="16"/>
-      <c r="C182" s="16"/>
+      <c r="A182" s="14"/>
+      <c r="B182" s="14"/>
+      <c r="C182" s="14"/>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
-      <c r="F182" s="16"/>
-      <c r="G182" s="16"/>
-      <c r="H182" s="45"/>
+      <c r="F182" s="14"/>
+      <c r="G182" s="14"/>
+      <c r="H182" s="43"/>
     </row>
     <row r="183" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="16"/>
-      <c r="B183" s="16"/>
-      <c r="C183" s="16"/>
+      <c r="A183" s="14"/>
+      <c r="B183" s="14"/>
+      <c r="C183" s="14"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
-      <c r="F183" s="16"/>
-      <c r="G183" s="16"/>
-      <c r="H183" s="45"/>
+      <c r="F183" s="14"/>
+      <c r="G183" s="14"/>
+      <c r="H183" s="43"/>
     </row>
     <row r="184" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="16"/>
-      <c r="B184" s="16"/>
-      <c r="C184" s="16"/>
+      <c r="A184" s="14"/>
+      <c r="B184" s="14"/>
+      <c r="C184" s="14"/>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
-      <c r="F184" s="16"/>
-      <c r="G184" s="16"/>
-      <c r="H184" s="45"/>
+      <c r="F184" s="14"/>
+      <c r="G184" s="14"/>
+      <c r="H184" s="43"/>
     </row>
     <row r="185" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="16"/>
-      <c r="B185" s="16"/>
-      <c r="C185" s="16"/>
+      <c r="A185" s="14"/>
+      <c r="B185" s="14"/>
+      <c r="C185" s="14"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
-      <c r="F185" s="16"/>
-      <c r="G185" s="16"/>
-      <c r="H185" s="45"/>
+      <c r="F185" s="14"/>
+      <c r="G185" s="14"/>
+      <c r="H185" s="43"/>
     </row>
     <row r="186" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="16"/>
-      <c r="B186" s="16"/>
-      <c r="C186" s="16"/>
+      <c r="A186" s="14"/>
+      <c r="B186" s="14"/>
+      <c r="C186" s="14"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
-      <c r="F186" s="16"/>
-      <c r="G186" s="16"/>
-      <c r="H186" s="45"/>
+      <c r="F186" s="14"/>
+      <c r="G186" s="14"/>
+      <c r="H186" s="43"/>
     </row>
     <row r="187" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="16"/>
-      <c r="B187" s="16"/>
-      <c r="C187" s="16"/>
+      <c r="A187" s="14"/>
+      <c r="B187" s="14"/>
+      <c r="C187" s="14"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
-      <c r="F187" s="16"/>
-      <c r="G187" s="16"/>
-      <c r="H187" s="45"/>
+      <c r="F187" s="14"/>
+      <c r="G187" s="14"/>
+      <c r="H187" s="43"/>
     </row>
     <row r="188" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="16"/>
-      <c r="B188" s="16"/>
-      <c r="C188" s="16"/>
+      <c r="A188" s="14"/>
+      <c r="B188" s="14"/>
+      <c r="C188" s="14"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
-      <c r="F188" s="16"/>
-      <c r="G188" s="16"/>
-      <c r="H188" s="45"/>
+      <c r="F188" s="14"/>
+      <c r="G188" s="14"/>
+      <c r="H188" s="43"/>
     </row>
     <row r="189" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="16"/>
-      <c r="B189" s="16"/>
-      <c r="C189" s="16"/>
+      <c r="A189" s="14"/>
+      <c r="B189" s="14"/>
+      <c r="C189" s="14"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
-      <c r="F189" s="16"/>
-      <c r="G189" s="16"/>
-      <c r="H189" s="45"/>
+      <c r="F189" s="14"/>
+      <c r="G189" s="14"/>
+      <c r="H189" s="43"/>
     </row>
     <row r="190" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="16"/>
-      <c r="B190" s="16"/>
-      <c r="C190" s="16"/>
+      <c r="A190" s="14"/>
+      <c r="B190" s="14"/>
+      <c r="C190" s="14"/>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
-      <c r="F190" s="16"/>
-      <c r="G190" s="16"/>
-      <c r="H190" s="45"/>
+      <c r="F190" s="14"/>
+      <c r="G190" s="14"/>
+      <c r="H190" s="43"/>
     </row>
     <row r="191" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="16"/>
-      <c r="B191" s="16"/>
-      <c r="C191" s="16"/>
+      <c r="A191" s="14"/>
+      <c r="B191" s="14"/>
+      <c r="C191" s="14"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
-      <c r="F191" s="16"/>
-      <c r="G191" s="16"/>
-      <c r="H191" s="45"/>
+      <c r="F191" s="14"/>
+      <c r="G191" s="14"/>
+      <c r="H191" s="43"/>
     </row>
     <row r="192" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="16"/>
-      <c r="B192" s="16"/>
-      <c r="C192" s="16"/>
+      <c r="A192" s="14"/>
+      <c r="B192" s="14"/>
+      <c r="C192" s="14"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
-      <c r="F192" s="16"/>
-      <c r="G192" s="16"/>
-      <c r="H192" s="45"/>
+      <c r="F192" s="14"/>
+      <c r="G192" s="14"/>
+      <c r="H192" s="43"/>
     </row>
     <row r="193" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="16"/>
-      <c r="B193" s="16"/>
-      <c r="C193" s="16"/>
+      <c r="A193" s="14"/>
+      <c r="B193" s="14"/>
+      <c r="C193" s="14"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
-      <c r="F193" s="16"/>
-      <c r="G193" s="16"/>
-      <c r="H193" s="45"/>
+      <c r="F193" s="14"/>
+      <c r="G193" s="14"/>
+      <c r="H193" s="43"/>
     </row>
     <row r="194" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="16"/>
-      <c r="B194" s="16"/>
-      <c r="C194" s="16"/>
+      <c r="A194" s="14"/>
+      <c r="B194" s="14"/>
+      <c r="C194" s="14"/>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
-      <c r="F194" s="16"/>
-      <c r="G194" s="16"/>
-      <c r="H194" s="45"/>
+      <c r="F194" s="14"/>
+      <c r="G194" s="14"/>
+      <c r="H194" s="43"/>
     </row>
     <row r="195" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="16"/>
-      <c r="B195" s="16"/>
-      <c r="C195" s="16"/>
+      <c r="A195" s="14"/>
+      <c r="B195" s="14"/>
+      <c r="C195" s="14"/>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
-      <c r="F195" s="16"/>
-      <c r="G195" s="16"/>
-      <c r="H195" s="45"/>
+      <c r="F195" s="14"/>
+      <c r="G195" s="14"/>
+      <c r="H195" s="43"/>
     </row>
     <row r="196" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="16"/>
-      <c r="B196" s="16"/>
-      <c r="C196" s="16"/>
+      <c r="A196" s="14"/>
+      <c r="B196" s="14"/>
+      <c r="C196" s="14"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
-      <c r="F196" s="16"/>
-      <c r="G196" s="16"/>
-      <c r="H196" s="45"/>
+      <c r="F196" s="14"/>
+      <c r="G196" s="14"/>
+      <c r="H196" s="43"/>
     </row>
     <row r="197" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="16"/>
-      <c r="B197" s="16"/>
-      <c r="C197" s="16"/>
+      <c r="A197" s="14"/>
+      <c r="B197" s="14"/>
+      <c r="C197" s="14"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
-      <c r="F197" s="16"/>
-      <c r="G197" s="16"/>
-      <c r="H197" s="45"/>
+      <c r="F197" s="14"/>
+      <c r="G197" s="14"/>
+      <c r="H197" s="43"/>
     </row>
     <row r="198" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="16"/>
-      <c r="B198" s="16"/>
-      <c r="C198" s="16"/>
+      <c r="A198" s="14"/>
+      <c r="B198" s="14"/>
+      <c r="C198" s="14"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
-      <c r="F198" s="16"/>
-      <c r="G198" s="16"/>
-      <c r="H198" s="45"/>
+      <c r="F198" s="14"/>
+      <c r="G198" s="14"/>
+      <c r="H198" s="43"/>
     </row>
     <row r="199" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="16"/>
-      <c r="B199" s="16"/>
-      <c r="C199" s="16"/>
+      <c r="A199" s="14"/>
+      <c r="B199" s="14"/>
+      <c r="C199" s="14"/>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
-      <c r="F199" s="16"/>
-      <c r="G199" s="16"/>
-      <c r="H199" s="45"/>
+      <c r="F199" s="14"/>
+      <c r="G199" s="14"/>
+      <c r="H199" s="43"/>
     </row>
     <row r="200" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="16"/>
-      <c r="B200" s="16"/>
-      <c r="C200" s="16"/>
+      <c r="A200" s="14"/>
+      <c r="B200" s="14"/>
+      <c r="C200" s="14"/>
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
-      <c r="F200" s="16"/>
-      <c r="G200" s="16"/>
-      <c r="H200" s="45"/>
+      <c r="F200" s="14"/>
+      <c r="G200" s="14"/>
+      <c r="H200" s="43"/>
     </row>
     <row r="201" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="16"/>
-      <c r="B201" s="16"/>
-      <c r="C201" s="16"/>
+      <c r="A201" s="14"/>
+      <c r="B201" s="14"/>
+      <c r="C201" s="14"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
-      <c r="F201" s="16"/>
-      <c r="G201" s="16"/>
-      <c r="H201" s="45"/>
+      <c r="F201" s="14"/>
+      <c r="G201" s="14"/>
+      <c r="H201" s="43"/>
     </row>
     <row r="202" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="16"/>
-      <c r="B202" s="16"/>
-      <c r="C202" s="16"/>
+      <c r="A202" s="14"/>
+      <c r="B202" s="14"/>
+      <c r="C202" s="14"/>
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
-      <c r="F202" s="16"/>
-      <c r="G202" s="16"/>
-      <c r="H202" s="45"/>
+      <c r="F202" s="14"/>
+      <c r="G202" s="14"/>
+      <c r="H202" s="43"/>
     </row>
     <row r="203" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="16"/>
-      <c r="B203" s="16"/>
-      <c r="C203" s="16"/>
+      <c r="A203" s="14"/>
+      <c r="B203" s="14"/>
+      <c r="C203" s="14"/>
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
-      <c r="F203" s="16"/>
-      <c r="G203" s="16"/>
-      <c r="H203" s="45"/>
+      <c r="F203" s="14"/>
+      <c r="G203" s="14"/>
+      <c r="H203" s="43"/>
     </row>
     <row r="204" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="16"/>
-      <c r="B204" s="16"/>
-      <c r="C204" s="16"/>
+      <c r="A204" s="14"/>
+      <c r="B204" s="14"/>
+      <c r="C204" s="14"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
-      <c r="F204" s="16"/>
-      <c r="G204" s="16"/>
-      <c r="H204" s="45"/>
+      <c r="F204" s="14"/>
+      <c r="G204" s="14"/>
+      <c r="H204" s="43"/>
     </row>
     <row r="205" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="16"/>
-      <c r="B205" s="16"/>
-      <c r="C205" s="16"/>
+      <c r="A205" s="14"/>
+      <c r="B205" s="14"/>
+      <c r="C205" s="14"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
-      <c r="F205" s="16"/>
-      <c r="G205" s="16"/>
-      <c r="H205" s="45"/>
+      <c r="F205" s="14"/>
+      <c r="G205" s="14"/>
+      <c r="H205" s="43"/>
     </row>
     <row r="206" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="16"/>
-      <c r="B206" s="16"/>
-      <c r="C206" s="16"/>
+      <c r="A206" s="14"/>
+      <c r="B206" s="14"/>
+      <c r="C206" s="14"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
-      <c r="F206" s="16"/>
-      <c r="G206" s="16"/>
-      <c r="H206" s="45"/>
+      <c r="F206" s="14"/>
+      <c r="G206" s="14"/>
+      <c r="H206" s="43"/>
     </row>
     <row r="207" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="16"/>
-      <c r="B207" s="16"/>
-      <c r="C207" s="16"/>
+      <c r="A207" s="14"/>
+      <c r="B207" s="14"/>
+      <c r="C207" s="14"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
-      <c r="F207" s="16"/>
-      <c r="G207" s="16"/>
-      <c r="H207" s="45"/>
+      <c r="F207" s="14"/>
+      <c r="G207" s="14"/>
+      <c r="H207" s="43"/>
     </row>
     <row r="208" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="16"/>
-      <c r="B208" s="16"/>
-      <c r="C208" s="16"/>
+      <c r="A208" s="14"/>
+      <c r="B208" s="14"/>
+      <c r="C208" s="14"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
-      <c r="F208" s="16"/>
-      <c r="G208" s="16"/>
-      <c r="H208" s="45"/>
+      <c r="F208" s="14"/>
+      <c r="G208" s="14"/>
+      <c r="H208" s="43"/>
     </row>
     <row r="209" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="16"/>
-      <c r="B209" s="16"/>
-      <c r="C209" s="16"/>
+      <c r="A209" s="14"/>
+      <c r="B209" s="14"/>
+      <c r="C209" s="14"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
-      <c r="F209" s="16"/>
-      <c r="G209" s="16"/>
-      <c r="H209" s="45"/>
+      <c r="F209" s="14"/>
+      <c r="G209" s="14"/>
+      <c r="H209" s="43"/>
     </row>
     <row r="210" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="16"/>
-      <c r="B210" s="16"/>
-      <c r="C210" s="16"/>
+      <c r="A210" s="14"/>
+      <c r="B210" s="14"/>
+      <c r="C210" s="14"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
-      <c r="F210" s="16"/>
-      <c r="G210" s="16"/>
-      <c r="H210" s="45"/>
+      <c r="F210" s="14"/>
+      <c r="G210" s="14"/>
+      <c r="H210" s="43"/>
     </row>
     <row r="211" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="16"/>
-      <c r="B211" s="16"/>
-      <c r="C211" s="16"/>
+      <c r="A211" s="14"/>
+      <c r="B211" s="14"/>
+      <c r="C211" s="14"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
-      <c r="F211" s="16"/>
-      <c r="G211" s="16"/>
-      <c r="H211" s="45"/>
+      <c r="F211" s="14"/>
+      <c r="G211" s="14"/>
+      <c r="H211" s="43"/>
     </row>
     <row r="212" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="16"/>
-      <c r="B212" s="16"/>
-      <c r="C212" s="16"/>
+      <c r="A212" s="14"/>
+      <c r="B212" s="14"/>
+      <c r="C212" s="14"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
-      <c r="F212" s="16"/>
-      <c r="G212" s="16"/>
-      <c r="H212" s="45"/>
+      <c r="F212" s="14"/>
+      <c r="G212" s="14"/>
+      <c r="H212" s="43"/>
     </row>
     <row r="213" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="16"/>
-      <c r="B213" s="16"/>
-      <c r="C213" s="16"/>
+      <c r="A213" s="14"/>
+      <c r="B213" s="14"/>
+      <c r="C213" s="14"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
-      <c r="F213" s="16"/>
-      <c r="G213" s="16"/>
-      <c r="H213" s="45"/>
+      <c r="F213" s="14"/>
+      <c r="G213" s="14"/>
+      <c r="H213" s="43"/>
     </row>
     <row r="214" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="16"/>
-      <c r="B214" s="16"/>
-      <c r="C214" s="16"/>
+      <c r="A214" s="14"/>
+      <c r="B214" s="14"/>
+      <c r="C214" s="14"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
-      <c r="F214" s="16"/>
-      <c r="G214" s="16"/>
-      <c r="H214" s="45"/>
+      <c r="F214" s="14"/>
+      <c r="G214" s="14"/>
+      <c r="H214" s="43"/>
     </row>
     <row r="215" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="16"/>
-      <c r="B215" s="16"/>
-      <c r="C215" s="16"/>
+      <c r="A215" s="14"/>
+      <c r="B215" s="14"/>
+      <c r="C215" s="14"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
-      <c r="F215" s="16"/>
-      <c r="G215" s="16"/>
-      <c r="H215" s="45"/>
+      <c r="F215" s="14"/>
+      <c r="G215" s="14"/>
+      <c r="H215" s="43"/>
     </row>
     <row r="216" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="16"/>
-      <c r="B216" s="16"/>
-      <c r="C216" s="16"/>
+      <c r="A216" s="14"/>
+      <c r="B216" s="14"/>
+      <c r="C216" s="14"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
-      <c r="F216" s="16"/>
-      <c r="G216" s="16"/>
-      <c r="H216" s="45"/>
+      <c r="F216" s="14"/>
+      <c r="G216" s="14"/>
+      <c r="H216" s="43"/>
     </row>
     <row r="217" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="16"/>
-      <c r="B217" s="16"/>
-      <c r="C217" s="16"/>
+      <c r="A217" s="14"/>
+      <c r="B217" s="14"/>
+      <c r="C217" s="14"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
-      <c r="F217" s="16"/>
-      <c r="G217" s="16"/>
-      <c r="H217" s="45"/>
+      <c r="F217" s="14"/>
+      <c r="G217" s="14"/>
+      <c r="H217" s="43"/>
     </row>
     <row r="218" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="16"/>
-      <c r="B218" s="16"/>
-      <c r="C218" s="16"/>
+      <c r="A218" s="14"/>
+      <c r="B218" s="14"/>
+      <c r="C218" s="14"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
-      <c r="F218" s="16"/>
-      <c r="G218" s="16"/>
-      <c r="H218" s="45"/>
+      <c r="F218" s="14"/>
+      <c r="G218" s="14"/>
+      <c r="H218" s="43"/>
     </row>
     <row r="219" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="16"/>
-      <c r="B219" s="16"/>
-      <c r="C219" s="16"/>
+      <c r="A219" s="14"/>
+      <c r="B219" s="14"/>
+      <c r="C219" s="14"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
-      <c r="F219" s="16"/>
-      <c r="G219" s="16"/>
-      <c r="H219" s="45"/>
+      <c r="F219" s="14"/>
+      <c r="G219" s="14"/>
+      <c r="H219" s="43"/>
     </row>
     <row r="220" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="16"/>
-      <c r="B220" s="16"/>
-      <c r="C220" s="16"/>
+      <c r="A220" s="14"/>
+      <c r="B220" s="14"/>
+      <c r="C220" s="14"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
-      <c r="F220" s="16"/>
-      <c r="G220" s="16"/>
-      <c r="H220" s="45"/>
+      <c r="F220" s="14"/>
+      <c r="G220" s="14"/>
+      <c r="H220" s="43"/>
     </row>
     <row r="221" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="16"/>
-      <c r="B221" s="16"/>
-      <c r="C221" s="16"/>
+      <c r="A221" s="14"/>
+      <c r="B221" s="14"/>
+      <c r="C221" s="14"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
-      <c r="F221" s="16"/>
-      <c r="G221" s="16"/>
-      <c r="H221" s="45"/>
+      <c r="F221" s="14"/>
+      <c r="G221" s="14"/>
+      <c r="H221" s="43"/>
     </row>
     <row r="222" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="16"/>
-      <c r="B222" s="16"/>
-      <c r="C222" s="16"/>
+      <c r="A222" s="14"/>
+      <c r="B222" s="14"/>
+      <c r="C222" s="14"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
-      <c r="F222" s="16"/>
-      <c r="G222" s="16"/>
-      <c r="H222" s="45"/>
+      <c r="F222" s="14"/>
+      <c r="G222" s="14"/>
+      <c r="H222" s="43"/>
     </row>
     <row r="223" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="16"/>
-      <c r="B223" s="16"/>
-      <c r="C223" s="16"/>
+      <c r="A223" s="14"/>
+      <c r="B223" s="14"/>
+      <c r="C223" s="14"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
-      <c r="F223" s="16"/>
-      <c r="G223" s="16"/>
-      <c r="H223" s="45"/>
+      <c r="F223" s="14"/>
+      <c r="G223" s="14"/>
+      <c r="H223" s="43"/>
     </row>
     <row r="224" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="16"/>
-      <c r="B224" s="16"/>
-      <c r="C224" s="16"/>
+      <c r="A224" s="14"/>
+      <c r="B224" s="14"/>
+      <c r="C224" s="14"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
-      <c r="F224" s="16"/>
-      <c r="G224" s="16"/>
-      <c r="H224" s="45"/>
+      <c r="F224" s="14"/>
+      <c r="G224" s="14"/>
+      <c r="H224" s="43"/>
     </row>
     <row r="225" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="16"/>
-      <c r="B225" s="16"/>
-      <c r="C225" s="16"/>
+      <c r="A225" s="14"/>
+      <c r="B225" s="14"/>
+      <c r="C225" s="14"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
-      <c r="F225" s="16"/>
-      <c r="G225" s="16"/>
-      <c r="H225" s="45"/>
+      <c r="F225" s="14"/>
+      <c r="G225" s="14"/>
+      <c r="H225" s="43"/>
     </row>
     <row r="226" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="16"/>
-      <c r="B226" s="16"/>
-      <c r="C226" s="16"/>
+      <c r="A226" s="14"/>
+      <c r="B226" s="14"/>
+      <c r="C226" s="14"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
-      <c r="F226" s="16"/>
-      <c r="G226" s="16"/>
-      <c r="H226" s="45"/>
+      <c r="F226" s="14"/>
+      <c r="G226" s="14"/>
+      <c r="H226" s="43"/>
     </row>
     <row r="227" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="16"/>
-      <c r="B227" s="16"/>
-      <c r="C227" s="16"/>
+      <c r="A227" s="14"/>
+      <c r="B227" s="14"/>
+      <c r="C227" s="14"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
-      <c r="F227" s="16"/>
-      <c r="G227" s="16"/>
-      <c r="H227" s="45"/>
+      <c r="F227" s="14"/>
+      <c r="G227" s="14"/>
+      <c r="H227" s="43"/>
     </row>
     <row r="228" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="16"/>
-      <c r="B228" s="16"/>
-      <c r="C228" s="16"/>
+      <c r="A228" s="14"/>
+      <c r="B228" s="14"/>
+      <c r="C228" s="14"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
-      <c r="F228" s="16"/>
-      <c r="G228" s="16"/>
-      <c r="H228" s="45"/>
+      <c r="F228" s="14"/>
+      <c r="G228" s="14"/>
+      <c r="H228" s="43"/>
     </row>
     <row r="229" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="16"/>
-      <c r="B229" s="16"/>
-      <c r="C229" s="16"/>
+      <c r="A229" s="14"/>
+      <c r="B229" s="14"/>
+      <c r="C229" s="14"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
-      <c r="F229" s="16"/>
-      <c r="G229" s="16"/>
-      <c r="H229" s="45"/>
+      <c r="F229" s="14"/>
+      <c r="G229" s="14"/>
+      <c r="H229" s="43"/>
     </row>
     <row r="230" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="16"/>
-      <c r="B230" s="16"/>
-      <c r="C230" s="16"/>
+      <c r="A230" s="14"/>
+      <c r="B230" s="14"/>
+      <c r="C230" s="14"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
-      <c r="F230" s="16"/>
-      <c r="G230" s="16"/>
-      <c r="H230" s="45"/>
+      <c r="F230" s="14"/>
+      <c r="G230" s="14"/>
+      <c r="H230" s="43"/>
     </row>
     <row r="231" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="16"/>
-      <c r="B231" s="16"/>
-      <c r="C231" s="16"/>
+      <c r="A231" s="14"/>
+      <c r="B231" s="14"/>
+      <c r="C231" s="14"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
-      <c r="F231" s="16"/>
-      <c r="G231" s="16"/>
-      <c r="H231" s="45"/>
+      <c r="F231" s="14"/>
+      <c r="G231" s="14"/>
+      <c r="H231" s="43"/>
     </row>
     <row r="232" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="16"/>
-      <c r="B232" s="16"/>
-      <c r="C232" s="16"/>
+      <c r="A232" s="14"/>
+      <c r="B232" s="14"/>
+      <c r="C232" s="14"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
-      <c r="F232" s="16"/>
-      <c r="G232" s="16"/>
-      <c r="H232" s="45"/>
+      <c r="F232" s="14"/>
+      <c r="G232" s="14"/>
+      <c r="H232" s="43"/>
     </row>
     <row r="233" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="16"/>
-      <c r="B233" s="16"/>
-      <c r="C233" s="16"/>
+      <c r="A233" s="14"/>
+      <c r="B233" s="14"/>
+      <c r="C233" s="14"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
-      <c r="F233" s="16"/>
-      <c r="G233" s="16"/>
-      <c r="H233" s="45"/>
+      <c r="F233" s="14"/>
+      <c r="G233" s="14"/>
+      <c r="H233" s="43"/>
     </row>
     <row r="234" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="16"/>
-      <c r="B234" s="16"/>
-      <c r="C234" s="16"/>
+      <c r="A234" s="14"/>
+      <c r="B234" s="14"/>
+      <c r="C234" s="14"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
-      <c r="F234" s="16"/>
-      <c r="G234" s="16"/>
-      <c r="H234" s="45"/>
+      <c r="F234" s="14"/>
+      <c r="G234" s="14"/>
+      <c r="H234" s="43"/>
     </row>
     <row r="235" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="16"/>
-      <c r="B235" s="16"/>
-      <c r="C235" s="16"/>
+      <c r="A235" s="14"/>
+      <c r="B235" s="14"/>
+      <c r="C235" s="14"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
-      <c r="F235" s="16"/>
-      <c r="G235" s="16"/>
-      <c r="H235" s="45"/>
+      <c r="F235" s="14"/>
+      <c r="G235" s="14"/>
+      <c r="H235" s="43"/>
     </row>
     <row r="236" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="16"/>
-      <c r="B236" s="16"/>
-      <c r="C236" s="16"/>
+      <c r="A236" s="14"/>
+      <c r="B236" s="14"/>
+      <c r="C236" s="14"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
-      <c r="F236" s="16"/>
-      <c r="G236" s="16"/>
-      <c r="H236" s="45"/>
+      <c r="F236" s="14"/>
+      <c r="G236" s="14"/>
+      <c r="H236" s="43"/>
     </row>
     <row r="237" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="16"/>
-      <c r="B237" s="16"/>
-      <c r="C237" s="16"/>
+      <c r="A237" s="14"/>
+      <c r="B237" s="14"/>
+      <c r="C237" s="14"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
-      <c r="F237" s="16"/>
-      <c r="G237" s="16"/>
-      <c r="H237" s="45"/>
+      <c r="F237" s="14"/>
+      <c r="G237" s="14"/>
+      <c r="H237" s="43"/>
     </row>
     <row r="238" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="16"/>
-      <c r="B238" s="16"/>
-      <c r="C238" s="16"/>
+      <c r="A238" s="14"/>
+      <c r="B238" s="14"/>
+      <c r="C238" s="14"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
-      <c r="F238" s="16"/>
-      <c r="G238" s="16"/>
-      <c r="H238" s="45"/>
+      <c r="F238" s="14"/>
+      <c r="G238" s="14"/>
+      <c r="H238" s="43"/>
     </row>
     <row r="239" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="16"/>
-      <c r="B239" s="16"/>
-      <c r="C239" s="16"/>
+      <c r="A239" s="14"/>
+      <c r="B239" s="14"/>
+      <c r="C239" s="14"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
-      <c r="F239" s="16"/>
-      <c r="G239" s="16"/>
-      <c r="H239" s="45"/>
+      <c r="F239" s="14"/>
+      <c r="G239" s="14"/>
+      <c r="H239" s="43"/>
     </row>
     <row r="240" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="16"/>
-      <c r="B240" s="16"/>
-      <c r="C240" s="16"/>
+      <c r="A240" s="14"/>
+      <c r="B240" s="14"/>
+      <c r="C240" s="14"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
-      <c r="F240" s="16"/>
-      <c r="G240" s="16"/>
-      <c r="H240" s="45"/>
+      <c r="F240" s="14"/>
+      <c r="G240" s="14"/>
+      <c r="H240" s="43"/>
     </row>
     <row r="241" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="16"/>
-      <c r="B241" s="16"/>
-      <c r="C241" s="16"/>
+      <c r="A241" s="14"/>
+      <c r="B241" s="14"/>
+      <c r="C241" s="14"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
-      <c r="F241" s="16"/>
-      <c r="G241" s="16"/>
-      <c r="H241" s="45"/>
+      <c r="F241" s="14"/>
+      <c r="G241" s="14"/>
+      <c r="H241" s="43"/>
     </row>
     <row r="242" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="16"/>
-      <c r="B242" s="16"/>
-      <c r="C242" s="16"/>
+      <c r="A242" s="14"/>
+      <c r="B242" s="14"/>
+      <c r="C242" s="14"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
-      <c r="F242" s="16"/>
-      <c r="G242" s="16"/>
-      <c r="H242" s="45"/>
+      <c r="F242" s="14"/>
+      <c r="G242" s="14"/>
+      <c r="H242" s="43"/>
     </row>
     <row r="243" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="16"/>
-      <c r="B243" s="16"/>
-      <c r="C243" s="16"/>
+      <c r="A243" s="14"/>
+      <c r="B243" s="14"/>
+      <c r="C243" s="14"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
-      <c r="F243" s="16"/>
-      <c r="G243" s="16"/>
-      <c r="H243" s="45"/>
+      <c r="F243" s="14"/>
+      <c r="G243" s="14"/>
+      <c r="H243" s="43"/>
     </row>
     <row r="244" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="16"/>
-      <c r="B244" s="16"/>
-      <c r="C244" s="16"/>
+      <c r="A244" s="14"/>
+      <c r="B244" s="14"/>
+      <c r="C244" s="14"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
-      <c r="F244" s="16"/>
-      <c r="G244" s="16"/>
-      <c r="H244" s="45"/>
+      <c r="F244" s="14"/>
+      <c r="G244" s="14"/>
+      <c r="H244" s="43"/>
     </row>
     <row r="245" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="16"/>
-      <c r="B245" s="16"/>
-      <c r="C245" s="16"/>
+      <c r="A245" s="14"/>
+      <c r="B245" s="14"/>
+      <c r="C245" s="14"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
-      <c r="F245" s="16"/>
-      <c r="G245" s="16"/>
-      <c r="H245" s="45"/>
+      <c r="F245" s="14"/>
+      <c r="G245" s="14"/>
+      <c r="H245" s="43"/>
     </row>
     <row r="246" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="16"/>
-      <c r="B246" s="16"/>
-      <c r="C246" s="16"/>
+      <c r="A246" s="14"/>
+      <c r="B246" s="14"/>
+      <c r="C246" s="14"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
-      <c r="F246" s="16"/>
-      <c r="G246" s="16"/>
-      <c r="H246" s="45"/>
+      <c r="F246" s="14"/>
+      <c r="G246" s="14"/>
+      <c r="H246" s="43"/>
     </row>
     <row r="247" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="16"/>
-      <c r="B247" s="16"/>
-      <c r="C247" s="16"/>
+      <c r="A247" s="14"/>
+      <c r="B247" s="14"/>
+      <c r="C247" s="14"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
-      <c r="F247" s="16"/>
-      <c r="G247" s="16"/>
-      <c r="H247" s="45"/>
+      <c r="F247" s="14"/>
+      <c r="G247" s="14"/>
+      <c r="H247" s="43"/>
     </row>
     <row r="248" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="16"/>
-      <c r="B248" s="16"/>
-      <c r="C248" s="16"/>
+      <c r="A248" s="14"/>
+      <c r="B248" s="14"/>
+      <c r="C248" s="14"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
-      <c r="F248" s="16"/>
-      <c r="G248" s="16"/>
-      <c r="H248" s="45"/>
+      <c r="F248" s="14"/>
+      <c r="G248" s="14"/>
+      <c r="H248" s="43"/>
     </row>
     <row r="249" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="16"/>
-      <c r="B249" s="16"/>
-      <c r="C249" s="16"/>
+      <c r="A249" s="14"/>
+      <c r="B249" s="14"/>
+      <c r="C249" s="14"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
-      <c r="F249" s="16"/>
-      <c r="G249" s="16"/>
-      <c r="H249" s="45"/>
+      <c r="F249" s="14"/>
+      <c r="G249" s="14"/>
+      <c r="H249" s="43"/>
     </row>
     <row r="250" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="16"/>
-      <c r="B250" s="16"/>
-      <c r="C250" s="16"/>
+      <c r="A250" s="14"/>
+      <c r="B250" s="14"/>
+      <c r="C250" s="14"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
-      <c r="F250" s="16"/>
-      <c r="G250" s="16"/>
-      <c r="H250" s="45"/>
+      <c r="F250" s="14"/>
+      <c r="G250" s="14"/>
+      <c r="H250" s="43"/>
     </row>
     <row r="251" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="16"/>
-      <c r="B251" s="16"/>
-      <c r="C251" s="16"/>
+      <c r="A251" s="14"/>
+      <c r="B251" s="14"/>
+      <c r="C251" s="14"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
-      <c r="F251" s="16"/>
-      <c r="G251" s="16"/>
-      <c r="H251" s="45"/>
+      <c r="F251" s="14"/>
+      <c r="G251" s="14"/>
+      <c r="H251" s="43"/>
     </row>
     <row r="252" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="16"/>
-      <c r="B252" s="16"/>
-      <c r="C252" s="16"/>
+      <c r="A252" s="14"/>
+      <c r="B252" s="14"/>
+      <c r="C252" s="14"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
-      <c r="F252" s="16"/>
-      <c r="G252" s="16"/>
-      <c r="H252" s="45"/>
+      <c r="F252" s="14"/>
+      <c r="G252" s="14"/>
+      <c r="H252" s="43"/>
     </row>
     <row r="253" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="16"/>
-      <c r="B253" s="16"/>
-      <c r="C253" s="16"/>
+      <c r="A253" s="14"/>
+      <c r="B253" s="14"/>
+      <c r="C253" s="14"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
-      <c r="F253" s="16"/>
-      <c r="G253" s="16"/>
-      <c r="H253" s="45"/>
+      <c r="F253" s="14"/>
+      <c r="G253" s="14"/>
+      <c r="H253" s="43"/>
     </row>
     <row r="254" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="16"/>
-      <c r="B254" s="16"/>
-      <c r="C254" s="16"/>
+      <c r="A254" s="14"/>
+      <c r="B254" s="14"/>
+      <c r="C254" s="14"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
-      <c r="F254" s="16"/>
-      <c r="G254" s="16"/>
-      <c r="H254" s="45"/>
+      <c r="F254" s="14"/>
+      <c r="G254" s="14"/>
+      <c r="H254" s="43"/>
     </row>
     <row r="255" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A255" s="16"/>
-      <c r="B255" s="16"/>
-      <c r="C255" s="16"/>
+      <c r="A255" s="14"/>
+      <c r="B255" s="14"/>
+      <c r="C255" s="14"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
-      <c r="F255" s="16"/>
-      <c r="G255" s="16"/>
-      <c r="H255" s="45"/>
+      <c r="F255" s="14"/>
+      <c r="G255" s="14"/>
+      <c r="H255" s="43"/>
     </row>
     <row r="256" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A256" s="16"/>
-      <c r="B256" s="16"/>
-      <c r="C256" s="16"/>
+      <c r="A256" s="14"/>
+      <c r="B256" s="14"/>
+      <c r="C256" s="14"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
-      <c r="F256" s="16"/>
-      <c r="G256" s="16"/>
-      <c r="H256" s="45"/>
+      <c r="F256" s="14"/>
+      <c r="G256" s="14"/>
+      <c r="H256" s="43"/>
     </row>
     <row r="257" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A257" s="16"/>
-      <c r="B257" s="16"/>
-      <c r="C257" s="16"/>
+      <c r="A257" s="14"/>
+      <c r="B257" s="14"/>
+      <c r="C257" s="14"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
-      <c r="F257" s="16"/>
-      <c r="G257" s="16"/>
-      <c r="H257" s="45"/>
+      <c r="F257" s="14"/>
+      <c r="G257" s="14"/>
+      <c r="H257" s="43"/>
     </row>
     <row r="258" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A258" s="16"/>
-      <c r="B258" s="16"/>
-      <c r="C258" s="16"/>
+      <c r="A258" s="14"/>
+      <c r="B258" s="14"/>
+      <c r="C258" s="14"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
-      <c r="F258" s="16"/>
-      <c r="G258" s="16"/>
-      <c r="H258" s="45"/>
+      <c r="F258" s="14"/>
+      <c r="G258" s="14"/>
+      <c r="H258" s="43"/>
     </row>
     <row r="259" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="16"/>
-      <c r="B259" s="16"/>
-      <c r="C259" s="16"/>
+      <c r="A259" s="14"/>
+      <c r="B259" s="14"/>
+      <c r="C259" s="14"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
-      <c r="F259" s="16"/>
-      <c r="G259" s="16"/>
-      <c r="H259" s="45"/>
+      <c r="F259" s="14"/>
+      <c r="G259" s="14"/>
+      <c r="H259" s="43"/>
     </row>
     <row r="260" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A260" s="16"/>
-      <c r="B260" s="16"/>
-      <c r="C260" s="16"/>
+      <c r="A260" s="14"/>
+      <c r="B260" s="14"/>
+      <c r="C260" s="14"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
-      <c r="F260" s="16"/>
-      <c r="G260" s="16"/>
-      <c r="H260" s="45"/>
+      <c r="F260" s="14"/>
+      <c r="G260" s="14"/>
+      <c r="H260" s="43"/>
     </row>
     <row r="261" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A261" s="16"/>
-      <c r="B261" s="16"/>
-      <c r="C261" s="16"/>
+      <c r="A261" s="14"/>
+      <c r="B261" s="14"/>
+      <c r="C261" s="14"/>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
-      <c r="F261" s="16"/>
-      <c r="G261" s="16"/>
-      <c r="H261" s="45"/>
+      <c r="F261" s="14"/>
+      <c r="G261" s="14"/>
+      <c r="H261" s="43"/>
     </row>
     <row r="262" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A262" s="16"/>
-      <c r="B262" s="16"/>
-      <c r="C262" s="16"/>
+      <c r="A262" s="14"/>
+      <c r="B262" s="14"/>
+      <c r="C262" s="14"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
-      <c r="F262" s="16"/>
-      <c r="G262" s="16"/>
-      <c r="H262" s="45"/>
+      <c r="F262" s="14"/>
+      <c r="G262" s="14"/>
+      <c r="H262" s="43"/>
     </row>
     <row r="263" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A263" s="16"/>
-      <c r="B263" s="16"/>
-      <c r="C263" s="16"/>
+      <c r="A263" s="14"/>
+      <c r="B263" s="14"/>
+      <c r="C263" s="14"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
-      <c r="F263" s="16"/>
-      <c r="G263" s="16"/>
-      <c r="H263" s="45"/>
+      <c r="F263" s="14"/>
+      <c r="G263" s="14"/>
+      <c r="H263" s="43"/>
     </row>
     <row r="264" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="16"/>
-      <c r="B264" s="16"/>
-      <c r="C264" s="16"/>
+      <c r="A264" s="14"/>
+      <c r="B264" s="14"/>
+      <c r="C264" s="14"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
-      <c r="F264" s="16"/>
-      <c r="G264" s="16"/>
-      <c r="H264" s="45"/>
+      <c r="F264" s="14"/>
+      <c r="G264" s="14"/>
+      <c r="H264" s="43"/>
     </row>
     <row r="265" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A265" s="16"/>
-      <c r="B265" s="16"/>
-      <c r="C265" s="16"/>
+      <c r="A265" s="14"/>
+      <c r="B265" s="14"/>
+      <c r="C265" s="14"/>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
-      <c r="F265" s="16"/>
-      <c r="G265" s="16"/>
-      <c r="H265" s="45"/>
+      <c r="F265" s="14"/>
+      <c r="G265" s="14"/>
+      <c r="H265" s="43"/>
     </row>
     <row r="266" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="16"/>
-      <c r="B266" s="16"/>
-      <c r="C266" s="16"/>
+      <c r="A266" s="14"/>
+      <c r="B266" s="14"/>
+      <c r="C266" s="14"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
-      <c r="F266" s="16"/>
-      <c r="G266" s="16"/>
-      <c r="H266" s="45"/>
+      <c r="F266" s="14"/>
+      <c r="G266" s="14"/>
+      <c r="H266" s="43"/>
     </row>
     <row r="267" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A267" s="16"/>
-      <c r="B267" s="16"/>
-      <c r="C267" s="16"/>
+      <c r="A267" s="14"/>
+      <c r="B267" s="14"/>
+      <c r="C267" s="14"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
-      <c r="F267" s="16"/>
-      <c r="G267" s="16"/>
-      <c r="H267" s="45"/>
+      <c r="F267" s="14"/>
+      <c r="G267" s="14"/>
+      <c r="H267" s="43"/>
     </row>
     <row r="268" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A268" s="16"/>
-      <c r="B268" s="16"/>
-      <c r="C268" s="16"/>
+      <c r="A268" s="14"/>
+      <c r="B268" s="14"/>
+      <c r="C268" s="14"/>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
-      <c r="F268" s="16"/>
-      <c r="G268" s="16"/>
-      <c r="H268" s="45"/>
+      <c r="F268" s="14"/>
+      <c r="G268" s="14"/>
+      <c r="H268" s="43"/>
     </row>
     <row r="269" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A269" s="16"/>
-      <c r="B269" s="16"/>
-      <c r="C269" s="16"/>
+      <c r="A269" s="14"/>
+      <c r="B269" s="14"/>
+      <c r="C269" s="14"/>
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
-      <c r="F269" s="16"/>
-      <c r="G269" s="16"/>
-      <c r="H269" s="45"/>
+      <c r="F269" s="14"/>
+      <c r="G269" s="14"/>
+      <c r="H269" s="43"/>
     </row>
     <row r="270" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A270" s="16"/>
-      <c r="B270" s="16"/>
-      <c r="C270" s="16"/>
+      <c r="A270" s="14"/>
+      <c r="B270" s="14"/>
+      <c r="C270" s="14"/>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
-      <c r="F270" s="16"/>
-      <c r="G270" s="16"/>
-      <c r="H270" s="45"/>
+      <c r="F270" s="14"/>
+      <c r="G270" s="14"/>
+      <c r="H270" s="43"/>
     </row>
     <row r="271" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="16"/>
-      <c r="B271" s="16"/>
-      <c r="C271" s="16"/>
+      <c r="A271" s="14"/>
+      <c r="B271" s="14"/>
+      <c r="C271" s="14"/>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
-      <c r="F271" s="16"/>
-      <c r="G271" s="16"/>
-      <c r="H271" s="45"/>
+      <c r="F271" s="14"/>
+      <c r="G271" s="14"/>
+      <c r="H271" s="43"/>
     </row>
     <row r="272" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A272" s="16"/>
-      <c r="B272" s="16"/>
-      <c r="C272" s="16"/>
+      <c r="A272" s="14"/>
+      <c r="B272" s="14"/>
+      <c r="C272" s="14"/>
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
-      <c r="F272" s="16"/>
-      <c r="G272" s="16"/>
-      <c r="H272" s="45"/>
+      <c r="F272" s="14"/>
+      <c r="G272" s="14"/>
+      <c r="H272" s="43"/>
     </row>
     <row r="273" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="16"/>
-      <c r="B273" s="16"/>
-      <c r="C273" s="16"/>
+      <c r="A273" s="14"/>
+      <c r="B273" s="14"/>
+      <c r="C273" s="14"/>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
-      <c r="F273" s="16"/>
-      <c r="G273" s="16"/>
-      <c r="H273" s="45"/>
+      <c r="F273" s="14"/>
+      <c r="G273" s="14"/>
+      <c r="H273" s="43"/>
     </row>
     <row r="274" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A274" s="16"/>
-      <c r="B274" s="16"/>
-      <c r="C274" s="16"/>
+      <c r="A274" s="14"/>
+      <c r="B274" s="14"/>
+      <c r="C274" s="14"/>
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
-      <c r="F274" s="16"/>
-      <c r="G274" s="16"/>
-      <c r="H274" s="45"/>
+      <c r="F274" s="14"/>
+      <c r="G274" s="14"/>
+      <c r="H274" s="43"/>
     </row>
     <row r="275" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A275" s="16"/>
-      <c r="B275" s="16"/>
-      <c r="C275" s="16"/>
+      <c r="A275" s="14"/>
+      <c r="B275" s="14"/>
+      <c r="C275" s="14"/>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
-      <c r="F275" s="16"/>
-      <c r="G275" s="16"/>
-      <c r="H275" s="45"/>
+      <c r="F275" s="14"/>
+      <c r="G275" s="14"/>
+      <c r="H275" s="43"/>
     </row>
     <row r="276" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A276" s="16"/>
-      <c r="B276" s="16"/>
-      <c r="C276" s="16"/>
+      <c r="A276" s="14"/>
+      <c r="B276" s="14"/>
+      <c r="C276" s="14"/>
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
-      <c r="F276" s="16"/>
-      <c r="G276" s="16"/>
-      <c r="H276" s="45"/>
+      <c r="F276" s="14"/>
+      <c r="G276" s="14"/>
+      <c r="H276" s="43"/>
     </row>
     <row r="277" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A277" s="16"/>
-      <c r="B277" s="16"/>
-      <c r="C277" s="16"/>
+      <c r="A277" s="14"/>
+      <c r="B277" s="14"/>
+      <c r="C277" s="14"/>
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
-      <c r="F277" s="16"/>
-      <c r="G277" s="16"/>
-      <c r="H277" s="45"/>
+      <c r="F277" s="14"/>
+      <c r="G277" s="14"/>
+      <c r="H277" s="43"/>
     </row>
     <row r="278" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A278" s="16"/>
-      <c r="B278" s="16"/>
-      <c r="C278" s="16"/>
+      <c r="A278" s="14"/>
+      <c r="B278" s="14"/>
+      <c r="C278" s="14"/>
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
-      <c r="F278" s="16"/>
-      <c r="G278" s="16"/>
-      <c r="H278" s="45"/>
+      <c r="F278" s="14"/>
+      <c r="G278" s="14"/>
+      <c r="H278" s="43"/>
     </row>
     <row r="279" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A279" s="16"/>
-      <c r="B279" s="16"/>
-      <c r="C279" s="16"/>
+      <c r="A279" s="14"/>
+      <c r="B279" s="14"/>
+      <c r="C279" s="14"/>
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
-      <c r="F279" s="16"/>
-      <c r="G279" s="16"/>
-      <c r="H279" s="45"/>
+      <c r="F279" s="14"/>
+      <c r="G279" s="14"/>
+      <c r="H279" s="43"/>
     </row>
     <row r="280" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="16"/>
-      <c r="B280" s="16"/>
-      <c r="C280" s="16"/>
+      <c r="A280" s="14"/>
+      <c r="B280" s="14"/>
+      <c r="C280" s="14"/>
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
-      <c r="F280" s="16"/>
-      <c r="G280" s="16"/>
-      <c r="H280" s="45"/>
+      <c r="F280" s="14"/>
+      <c r="G280" s="14"/>
+      <c r="H280" s="43"/>
     </row>
     <row r="281" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A281" s="16"/>
-      <c r="B281" s="16"/>
-      <c r="C281" s="16"/>
+      <c r="A281" s="14"/>
+      <c r="B281" s="14"/>
+      <c r="C281" s="14"/>
       <c r="D281" s="4"/>
       <c r="E281" s="4"/>
-      <c r="F281" s="16"/>
-      <c r="G281" s="16"/>
-      <c r="H281" s="45"/>
+      <c r="F281" s="14"/>
+      <c r="G281" s="14"/>
+      <c r="H281" s="43"/>
     </row>
     <row r="282" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A282" s="16"/>
-      <c r="B282" s="16"/>
-      <c r="C282" s="16"/>
+      <c r="A282" s="14"/>
+      <c r="B282" s="14"/>
+      <c r="C282" s="14"/>
       <c r="D282" s="4"/>
       <c r="E282" s="4"/>
-      <c r="F282" s="16"/>
-      <c r="G282" s="16"/>
-      <c r="H282" s="45"/>
+      <c r="F282" s="14"/>
+      <c r="G282" s="14"/>
+      <c r="H282" s="43"/>
     </row>
     <row r="283" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="16"/>
-      <c r="B283" s="16"/>
-      <c r="C283" s="16"/>
+      <c r="A283" s="14"/>
+      <c r="B283" s="14"/>
+      <c r="C283" s="14"/>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
-      <c r="F283" s="16"/>
-      <c r="G283" s="16"/>
-      <c r="H283" s="45"/>
+      <c r="F283" s="14"/>
+      <c r="G283" s="14"/>
+      <c r="H283" s="43"/>
     </row>
     <row r="284" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A284" s="16"/>
-      <c r="B284" s="16"/>
-      <c r="C284" s="16"/>
+      <c r="A284" s="14"/>
+      <c r="B284" s="14"/>
+      <c r="C284" s="14"/>
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
-      <c r="F284" s="16"/>
-      <c r="G284" s="16"/>
-      <c r="H284" s="45"/>
+      <c r="F284" s="14"/>
+      <c r="G284" s="14"/>
+      <c r="H284" s="43"/>
     </row>
     <row r="285" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A285" s="16"/>
-      <c r="B285" s="16"/>
-      <c r="C285" s="16"/>
+      <c r="A285" s="14"/>
+      <c r="B285" s="14"/>
+      <c r="C285" s="14"/>
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
-      <c r="F285" s="16"/>
-      <c r="G285" s="16"/>
-      <c r="H285" s="45"/>
+      <c r="F285" s="14"/>
+      <c r="G285" s="14"/>
+      <c r="H285" s="43"/>
     </row>
     <row r="286" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A286" s="16"/>
-      <c r="B286" s="16"/>
-      <c r="C286" s="16"/>
+      <c r="A286" s="14"/>
+      <c r="B286" s="14"/>
+      <c r="C286" s="14"/>
       <c r="D286" s="4"/>
       <c r="E286" s="4"/>
-      <c r="F286" s="16"/>
-      <c r="G286" s="16"/>
-      <c r="H286" s="45"/>
+      <c r="F286" s="14"/>
+      <c r="G286" s="14"/>
+      <c r="H286" s="43"/>
     </row>
     <row r="287" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="16"/>
-      <c r="B287" s="16"/>
-      <c r="C287" s="16"/>
+      <c r="A287" s="14"/>
+      <c r="B287" s="14"/>
+      <c r="C287" s="14"/>
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
-      <c r="F287" s="16"/>
-      <c r="G287" s="16"/>
-      <c r="H287" s="45"/>
+      <c r="F287" s="14"/>
+      <c r="G287" s="14"/>
+      <c r="H287" s="43"/>
     </row>
     <row r="288" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="16"/>
-      <c r="B288" s="16"/>
-      <c r="C288" s="16"/>
+      <c r="A288" s="14"/>
+      <c r="B288" s="14"/>
+      <c r="C288" s="14"/>
       <c r="D288" s="4"/>
       <c r="E288" s="4"/>
-      <c r="F288" s="16"/>
-      <c r="G288" s="16"/>
-      <c r="H288" s="45"/>
+      <c r="F288" s="14"/>
+      <c r="G288" s="14"/>
+      <c r="H288" s="43"/>
     </row>
     <row r="289" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A289" s="16"/>
-      <c r="B289" s="16"/>
-      <c r="C289" s="16"/>
+      <c r="A289" s="14"/>
+      <c r="B289" s="14"/>
+      <c r="C289" s="14"/>
       <c r="D289" s="4"/>
       <c r="E289" s="4"/>
-      <c r="F289" s="16"/>
-      <c r="G289" s="16"/>
-      <c r="H289" s="45"/>
+      <c r="F289" s="14"/>
+      <c r="G289" s="14"/>
+      <c r="H289" s="43"/>
     </row>
     <row r="290" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A290" s="16"/>
-      <c r="B290" s="16"/>
-      <c r="C290" s="16"/>
+      <c r="A290" s="14"/>
+      <c r="B290" s="14"/>
+      <c r="C290" s="14"/>
       <c r="D290" s="4"/>
       <c r="E290" s="4"/>
-      <c r="F290" s="16"/>
-      <c r="G290" s="16"/>
-      <c r="H290" s="45"/>
+      <c r="F290" s="14"/>
+      <c r="G290" s="14"/>
+      <c r="H290" s="43"/>
     </row>
     <row r="291" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A291" s="16"/>
-      <c r="B291" s="16"/>
-      <c r="C291" s="16"/>
+      <c r="A291" s="14"/>
+      <c r="B291" s="14"/>
+      <c r="C291" s="14"/>
       <c r="D291" s="4"/>
       <c r="E291" s="4"/>
-      <c r="F291" s="16"/>
-      <c r="G291" s="16"/>
-      <c r="H291" s="45"/>
+      <c r="F291" s="14"/>
+      <c r="G291" s="14"/>
+      <c r="H291" s="43"/>
     </row>
     <row r="292" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="16"/>
-      <c r="B292" s="16"/>
-      <c r="C292" s="16"/>
+      <c r="A292" s="14"/>
+      <c r="B292" s="14"/>
+      <c r="C292" s="14"/>
       <c r="D292" s="4"/>
       <c r="E292" s="4"/>
-      <c r="F292" s="16"/>
-      <c r="G292" s="16"/>
-      <c r="H292" s="45"/>
+      <c r="F292" s="14"/>
+      <c r="G292" s="14"/>
+      <c r="H292" s="43"/>
     </row>
     <row r="293" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A293" s="16"/>
-      <c r="B293" s="16"/>
-      <c r="C293" s="16"/>
+      <c r="A293" s="14"/>
+      <c r="B293" s="14"/>
+      <c r="C293" s="14"/>
       <c r="D293" s="4"/>
       <c r="E293" s="4"/>
-      <c r="F293" s="16"/>
-      <c r="G293" s="16"/>
-      <c r="H293" s="45"/>
+      <c r="F293" s="14"/>
+      <c r="G293" s="14"/>
+      <c r="H293" s="43"/>
     </row>
     <row r="294" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A294" s="16"/>
-      <c r="B294" s="16"/>
-      <c r="C294" s="16"/>
+      <c r="A294" s="14"/>
+      <c r="B294" s="14"/>
+      <c r="C294" s="14"/>
       <c r="D294" s="4"/>
       <c r="E294" s="4"/>
-      <c r="F294" s="16"/>
-      <c r="G294" s="16"/>
-      <c r="H294" s="45"/>
+      <c r="F294" s="14"/>
+      <c r="G294" s="14"/>
+      <c r="H294" s="43"/>
     </row>
     <row r="295" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="296" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5803,26 +5824,120 @@
     <row r="1011" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1012" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="156">
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A16:B16"/>
+  <mergeCells count="157">
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A94:H94"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="G82:H82"/>
+    <mergeCell ref="A83:H83"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="E84:F84"/>
+    <mergeCell ref="G84:H84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="E85:F85"/>
+    <mergeCell ref="G85:H85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="G86:H86"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="A93:H93"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A78:C78"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A65:C65"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B8:D8"/>
@@ -5847,119 +5962,26 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="A63:C63"/>
-    <mergeCell ref="A64:C64"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="A78:C78"/>
-    <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A94:H94"/>
-    <mergeCell ref="A80:C80"/>
-    <mergeCell ref="A81:H81"/>
-    <mergeCell ref="A82:C82"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="G82:H82"/>
-    <mergeCell ref="A83:H83"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="F69:G69"/>
-    <mergeCell ref="F70:G70"/>
-    <mergeCell ref="E84:F84"/>
-    <mergeCell ref="G84:H84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="E85:F85"/>
-    <mergeCell ref="G85:H85"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="G86:H86"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="A93:H93"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="A44:C44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F55:G55"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A38:C38"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A16:B16"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.11811023622047245" top="0.55118110236220474" bottom="0.55118110236220474" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1"/>
